--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T10:23:38+00:00</t>
+    <t>2025-02-24T13:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:55:23+00:00</t>
+    <t>2025-02-26T08:56:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T08:56:44+00:00</t>
+    <t>2025-03-04T11:06:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T11:06:18+00:00</t>
+    <t>2025-03-06T12:24:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T12:24:43+00:00</t>
+    <t>2025-03-20T12:28:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-20T12:28:15+00:00</t>
+    <t>2025-03-24T06:28:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-composition</t>
+    <t>https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-composition</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T06:28:05+00:00</t>
+    <t>2025-03-24T07:27:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -461,7 +461,7 @@
     <t>countryOfAffiliation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/country-of-affiliation}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/elga/aps/r4/StructureDefinition/country-of-affiliation}
 </t>
   </si>
   <si>
@@ -645,7 +645,7 @@
     <t>Composition.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-patient)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient)
 </t>
   </si>
   <si>
@@ -1043,7 +1043,7 @@
   </si>
   <si>
     <t>Identifier
-Reference(Composition|https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-composition)</t>
+Reference(Composition|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-composition)</t>
   </si>
   <si>
     <t>Target of the relationship</t>
@@ -1436,7 +1436,7 @@
     <t>medicationStatement</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-medicationstatement)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medicationstatement)
 </t>
   </si>
   <si>
@@ -1446,7 +1446,7 @@
     <t>medicationRequest</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-medicationrequest)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medicationrequest)
 </t>
   </si>
   <si>
@@ -1513,7 +1513,7 @@
     <t>allergyOrIntolerance</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-allergyintolerance)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-allergyintolerance)
 </t>
   </si>
   <si>
@@ -1580,7 +1580,7 @@
     <t>problem</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-condition)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-condition)
 </t>
   </si>
   <si>
@@ -1651,7 +1651,7 @@
     <t>procedure</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-Procedure)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-Procedure)
 </t>
   </si>
   <si>
@@ -1718,7 +1718,7 @@
     <t>deviceStatement</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-deviceusestatement)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-deviceusestatement)
 </t>
   </si>
   <si>
@@ -1785,7 +1785,7 @@
     <t>immunization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-immunization)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-immunization)
 </t>
   </si>
   <si>
@@ -1856,7 +1856,7 @@
     <t>resultsObservationLaboratoryPathology</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-observationresultslaboratorypathology)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observationresultslaboratorypathology)
 </t>
   </si>
   <si>
@@ -1866,7 +1866,7 @@
     <t>resultsObservationRadiology</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-observationresultsradiology)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observationresultsradiology)
 </t>
   </si>
   <si>
@@ -1876,7 +1876,7 @@
     <t>resultsDiagnosticReport</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-diagnosticreport)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-diagnosticreport)
 </t>
   </si>
   <si>
@@ -1943,7 +1943,7 @@
     <t>vitalSign</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-observationvitalsigns)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observationvitalsigns)
 </t>
   </si>
   <si>
@@ -2205,7 +2205,7 @@
     <t>smokingTobaccoUse</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-observationtobaccouse)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observationtobaccouse)
 </t>
   </si>
   <si>
@@ -2215,7 +2215,7 @@
     <t>alcoholUse</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-observationalcoholuse)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observationalcoholuse)
 </t>
   </si>
   <si>
@@ -2278,7 +2278,7 @@
     <t>pregnancyStatus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-observationpregnancystatus)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observationpregnancystatus)
 </t>
   </si>
   <si>
@@ -2288,7 +2288,7 @@
     <t>pregnancyOutcomeSummary</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga-austrianpatientsummary-r4/StructureDefinition/at-aps-observationpregnancyoutcome)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observationpregnancyoutcome)
 </t>
   </si>
   <si>
@@ -2797,7 +2797,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="118.54296875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="112.29296875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T07:27:46+00:00</t>
+    <t>2025-03-24T07:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-18T10:23:29+00:00</t>
+    <t>2026-01-28T10:05:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -905,7 +905,7 @@
     <t>Composition.attester.party</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|RelatedPerson|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization)
 </t>
   </si>
   <si>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11883" uniqueCount="790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11883" uniqueCount="789">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T10:05:57+00:00</t>
+    <t>2026-01-29T06:33:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1136,7 +1136,7 @@
 </t>
   </si>
   <si>
-    <t>openAtEnd</t>
+    <t>open</t>
   </si>
   <si>
     <t>cmp-1:A section must contain at least one of text, entries, or sub-sections {text.exists() or entry.exists() or section.exists()}
@@ -1404,9 +1404,6 @@
   <si>
     <t xml:space="preserve">profile:resolve()}
 </t>
-  </si>
-  <si>
-    <t>closed</t>
   </si>
   <si>
     <t>Composition.section:sectionMedications.entry:medicationStatement</t>
@@ -7784,7 +7781,7 @@
       </c>
       <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE42" t="s" s="2">
         <v>363</v>
@@ -10725,10 +10722,10 @@
       </c>
       <c r="AC67" s="2"/>
       <c r="AD67" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>449</v>
+        <v>363</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>413</v>
@@ -10763,13 +10760,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>79</v>
@@ -10791,7 +10788,7 @@
         <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>414</v>
@@ -10882,13 +10879,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>79</v>
@@ -10910,7 +10907,7 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L69" t="s" s="2">
         <v>414</v>
@@ -11001,13 +10998,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D70" t="s" s="2">
         <v>79</v>
@@ -11029,7 +11026,7 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L70" t="s" s="2">
         <v>414</v>
@@ -11120,13 +11117,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D71" t="s" s="2">
         <v>79</v>
@@ -11148,7 +11145,7 @@
         <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L71" t="s" s="2">
         <v>414</v>
@@ -11239,13 +11236,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>79</v>
@@ -11267,7 +11264,7 @@
         <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L72" t="s" s="2">
         <v>414</v>
@@ -11358,7 +11355,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>420</v>
@@ -11477,7 +11474,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>428</v>
@@ -11594,13 +11591,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>79</v>
@@ -11711,7 +11708,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>367</v>
@@ -11826,7 +11823,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>368</v>
@@ -11943,7 +11940,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>369</v>
@@ -12062,7 +12059,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>370</v>
@@ -12181,7 +12178,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>376</v>
@@ -12229,7 +12226,7 @@
         <v>79</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>79</v>
@@ -12300,7 +12297,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>383</v>
@@ -12417,7 +12414,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>386</v>
@@ -12534,7 +12531,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>391</v>
@@ -12651,7 +12648,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>397</v>
@@ -12770,7 +12767,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>405</v>
@@ -12889,7 +12886,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B86" t="s" s="2">
         <v>413</v>
@@ -12915,7 +12912,7 @@
         <v>79</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="L86" t="s" s="2">
         <v>414</v>
@@ -12966,10 +12963,10 @@
       </c>
       <c r="AC86" s="2"/>
       <c r="AD86" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>449</v>
+        <v>363</v>
       </c>
       <c r="AF86" t="s" s="2">
         <v>413</v>
@@ -13004,13 +13001,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>79</v>
@@ -13032,7 +13029,7 @@
         <v>79</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="L87" t="s" s="2">
         <v>414</v>
@@ -13123,13 +13120,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>79</v>
@@ -13151,7 +13148,7 @@
         <v>79</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L88" t="s" s="2">
         <v>414</v>
@@ -13242,7 +13239,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>420</v>
@@ -13361,7 +13358,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>428</v>
@@ -13478,13 +13475,13 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D91" t="s" s="2">
         <v>79</v>
@@ -13595,7 +13592,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>367</v>
@@ -13710,7 +13707,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>368</v>
@@ -13827,7 +13824,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>369</v>
@@ -13946,7 +13943,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>370</v>
@@ -14065,7 +14062,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B96" t="s" s="2">
         <v>376</v>
@@ -14113,7 +14110,7 @@
         <v>79</v>
       </c>
       <c r="S96" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T96" t="s" s="2">
         <v>79</v>
@@ -14184,7 +14181,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B97" t="s" s="2">
         <v>383</v>
@@ -14301,7 +14298,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>386</v>
@@ -14418,7 +14415,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>391</v>
@@ -14535,7 +14532,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>397</v>
@@ -14654,7 +14651,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>405</v>
@@ -14773,7 +14770,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>413</v>
@@ -14799,7 +14796,7 @@
         <v>79</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="L102" t="s" s="2">
         <v>414</v>
@@ -14850,10 +14847,10 @@
       </c>
       <c r="AC102" s="2"/>
       <c r="AD102" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>449</v>
+        <v>363</v>
       </c>
       <c r="AF102" t="s" s="2">
         <v>413</v>
@@ -14888,13 +14885,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>79</v>
@@ -14916,7 +14913,7 @@
         <v>79</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L103" t="s" s="2">
         <v>414</v>
@@ -15007,13 +15004,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>79</v>
@@ -15035,7 +15032,7 @@
         <v>79</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L104" t="s" s="2">
         <v>414</v>
@@ -15126,7 +15123,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>420</v>
@@ -15245,7 +15242,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>428</v>
@@ -15362,13 +15359,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D107" t="s" s="2">
         <v>79</v>
@@ -15459,7 +15456,7 @@
         <v>79</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>79</v>
@@ -15479,7 +15476,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>367</v>
@@ -15594,7 +15591,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>368</v>
@@ -15711,7 +15708,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>369</v>
@@ -15830,7 +15827,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B111" t="s" s="2">
         <v>370</v>
@@ -15949,7 +15946,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>376</v>
@@ -15997,7 +15994,7 @@
         <v>79</v>
       </c>
       <c r="S112" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="T112" t="s" s="2">
         <v>79</v>
@@ -16068,7 +16065,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>383</v>
@@ -16185,7 +16182,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>386</v>
@@ -16302,7 +16299,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>391</v>
@@ -16419,7 +16416,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>397</v>
@@ -16538,7 +16535,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>405</v>
@@ -16657,7 +16654,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>413</v>
@@ -16683,7 +16680,7 @@
         <v>79</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L118" t="s" s="2">
         <v>414</v>
@@ -16734,10 +16731,10 @@
       </c>
       <c r="AC118" s="2"/>
       <c r="AD118" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE118" t="s" s="2">
-        <v>449</v>
+        <v>363</v>
       </c>
       <c r="AF118" t="s" s="2">
         <v>413</v>
@@ -16772,13 +16769,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>79</v>
@@ -16800,7 +16797,7 @@
         <v>79</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="L119" t="s" s="2">
         <v>414</v>
@@ -16891,13 +16888,13 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D120" t="s" s="2">
         <v>79</v>
@@ -16919,7 +16916,7 @@
         <v>79</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L120" t="s" s="2">
         <v>414</v>
@@ -17010,7 +17007,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>420</v>
@@ -17129,7 +17126,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>428</v>
@@ -17246,13 +17243,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>79</v>
@@ -17343,7 +17340,7 @@
         <v>79</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>79</v>
@@ -17363,7 +17360,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>367</v>
@@ -17478,7 +17475,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>368</v>
@@ -17595,7 +17592,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>369</v>
@@ -17714,7 +17711,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>370</v>
@@ -17833,7 +17830,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>376</v>
@@ -17881,7 +17878,7 @@
         <v>79</v>
       </c>
       <c r="S128" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="T128" t="s" s="2">
         <v>79</v>
@@ -17952,7 +17949,7 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>383</v>
@@ -18069,7 +18066,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>386</v>
@@ -18186,7 +18183,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>391</v>
@@ -18303,7 +18300,7 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>397</v>
@@ -18422,7 +18419,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>405</v>
@@ -18541,7 +18538,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>413</v>
@@ -18567,7 +18564,7 @@
         <v>79</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="L134" t="s" s="2">
         <v>414</v>
@@ -18618,10 +18615,10 @@
       </c>
       <c r="AC134" s="2"/>
       <c r="AD134" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE134" t="s" s="2">
-        <v>449</v>
+        <v>363</v>
       </c>
       <c r="AF134" t="s" s="2">
         <v>413</v>
@@ -18656,13 +18653,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="D135" t="s" s="2">
         <v>79</v>
@@ -18684,7 +18681,7 @@
         <v>79</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="L135" t="s" s="2">
         <v>414</v>
@@ -18775,13 +18772,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D136" t="s" s="2">
         <v>79</v>
@@ -18803,7 +18800,7 @@
         <v>79</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L136" t="s" s="2">
         <v>414</v>
@@ -18894,7 +18891,7 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>420</v>
@@ -19013,7 +19010,7 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>428</v>
@@ -19130,13 +19127,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D139" t="s" s="2">
         <v>79</v>
@@ -19247,7 +19244,7 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>367</v>
@@ -19362,7 +19359,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>368</v>
@@ -19479,7 +19476,7 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>369</v>
@@ -19598,7 +19595,7 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>370</v>
@@ -19717,7 +19714,7 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>376</v>
@@ -19765,7 +19762,7 @@
         <v>79</v>
       </c>
       <c r="S144" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="T144" t="s" s="2">
         <v>79</v>
@@ -19836,7 +19833,7 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>383</v>
@@ -19953,7 +19950,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>386</v>
@@ -20070,7 +20067,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>391</v>
@@ -20187,7 +20184,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>397</v>
@@ -20306,7 +20303,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>405</v>
@@ -20425,7 +20422,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>413</v>
@@ -20451,7 +20448,7 @@
         <v>79</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="L150" t="s" s="2">
         <v>414</v>
@@ -20502,10 +20499,10 @@
       </c>
       <c r="AC150" s="2"/>
       <c r="AD150" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE150" t="s" s="2">
-        <v>449</v>
+        <v>363</v>
       </c>
       <c r="AF150" t="s" s="2">
         <v>413</v>
@@ -20540,13 +20537,13 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D151" t="s" s="2">
         <v>79</v>
@@ -20568,7 +20565,7 @@
         <v>79</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="L151" t="s" s="2">
         <v>414</v>
@@ -20659,13 +20656,13 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>79</v>
@@ -20687,7 +20684,7 @@
         <v>79</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L152" t="s" s="2">
         <v>414</v>
@@ -20778,7 +20775,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>420</v>
@@ -20897,7 +20894,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>428</v>
@@ -21014,13 +21011,13 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D155" t="s" s="2">
         <v>79</v>
@@ -21131,7 +21128,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>367</v>
@@ -21246,7 +21243,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>368</v>
@@ -21363,7 +21360,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>369</v>
@@ -21482,7 +21479,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>370</v>
@@ -21601,7 +21598,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>376</v>
@@ -21649,7 +21646,7 @@
         <v>79</v>
       </c>
       <c r="S160" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="T160" t="s" s="2">
         <v>79</v>
@@ -21720,7 +21717,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>383</v>
@@ -21837,7 +21834,7 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>386</v>
@@ -21954,7 +21951,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>391</v>
@@ -22071,7 +22068,7 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>397</v>
@@ -22190,7 +22187,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>405</v>
@@ -22309,7 +22306,7 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B166" t="s" s="2">
         <v>413</v>
@@ -22335,7 +22332,7 @@
         <v>79</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="L166" t="s" s="2">
         <v>414</v>
@@ -22382,11 +22379,11 @@
         <v>79</v>
       </c>
       <c r="AB166" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AC166" s="2"/>
       <c r="AD166" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE166" t="s" s="2">
         <v>363</v>
@@ -22424,13 +22421,13 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D167" t="s" s="2">
         <v>79</v>
@@ -22452,7 +22449,7 @@
         <v>79</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="L167" t="s" s="2">
         <v>414</v>
@@ -22543,13 +22540,13 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D168" t="s" s="2">
         <v>79</v>
@@ -22571,7 +22568,7 @@
         <v>79</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="L168" t="s" s="2">
         <v>414</v>
@@ -22662,13 +22659,13 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D169" t="s" s="2">
         <v>79</v>
@@ -22690,7 +22687,7 @@
         <v>79</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="L169" t="s" s="2">
         <v>414</v>
@@ -22781,13 +22778,13 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D170" t="s" s="2">
         <v>79</v>
@@ -22809,7 +22806,7 @@
         <v>79</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L170" t="s" s="2">
         <v>414</v>
@@ -22900,7 +22897,7 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>420</v>
@@ -23019,7 +23016,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>428</v>
@@ -23136,13 +23133,13 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D173" t="s" s="2">
         <v>79</v>
@@ -23253,7 +23250,7 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>367</v>
@@ -23368,7 +23365,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>368</v>
@@ -23485,7 +23482,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>369</v>
@@ -23604,7 +23601,7 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>370</v>
@@ -23723,7 +23720,7 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>376</v>
@@ -23771,7 +23768,7 @@
         <v>79</v>
       </c>
       <c r="S178" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="T178" t="s" s="2">
         <v>79</v>
@@ -23842,7 +23839,7 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>383</v>
@@ -23959,7 +23956,7 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>386</v>
@@ -24076,7 +24073,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>391</v>
@@ -24193,7 +24190,7 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B182" t="s" s="2">
         <v>397</v>
@@ -24312,7 +24309,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>405</v>
@@ -24431,7 +24428,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>413</v>
@@ -24457,7 +24454,7 @@
         <v>79</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L184" t="s" s="2">
         <v>414</v>
@@ -24508,7 +24505,7 @@
       </c>
       <c r="AC184" s="2"/>
       <c r="AD184" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE184" t="s" s="2">
         <v>363</v>
@@ -24546,13 +24543,13 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D185" t="s" s="2">
         <v>79</v>
@@ -24574,7 +24571,7 @@
         <v>79</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="L185" t="s" s="2">
         <v>414</v>
@@ -24665,13 +24662,13 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D186" t="s" s="2">
         <v>79</v>
@@ -24693,7 +24690,7 @@
         <v>79</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L186" t="s" s="2">
         <v>414</v>
@@ -24784,7 +24781,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B187" t="s" s="2">
         <v>420</v>
@@ -24903,7 +24900,7 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B188" t="s" s="2">
         <v>428</v>
@@ -25020,13 +25017,13 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B189" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D189" t="s" s="2">
         <v>79</v>
@@ -25137,7 +25134,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B190" t="s" s="2">
         <v>367</v>
@@ -25252,7 +25249,7 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B191" t="s" s="2">
         <v>368</v>
@@ -25369,7 +25366,7 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B192" t="s" s="2">
         <v>369</v>
@@ -25488,7 +25485,7 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B193" t="s" s="2">
         <v>370</v>
@@ -25607,7 +25604,7 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B194" t="s" s="2">
         <v>376</v>
@@ -25655,7 +25652,7 @@
         <v>79</v>
       </c>
       <c r="S194" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="T194" t="s" s="2">
         <v>79</v>
@@ -25726,7 +25723,7 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B195" t="s" s="2">
         <v>383</v>
@@ -25843,7 +25840,7 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>386</v>
@@ -25960,7 +25957,7 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>391</v>
@@ -26077,7 +26074,7 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>397</v>
@@ -26196,7 +26193,7 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>405</v>
@@ -26315,7 +26312,7 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B200" t="s" s="2">
         <v>413</v>
@@ -26341,7 +26338,7 @@
         <v>79</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="L200" t="s" s="2">
         <v>414</v>
@@ -26392,10 +26389,10 @@
       </c>
       <c r="AC200" s="2"/>
       <c r="AD200" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE200" t="s" s="2">
-        <v>449</v>
+        <v>363</v>
       </c>
       <c r="AF200" t="s" s="2">
         <v>413</v>
@@ -26430,13 +26427,13 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B201" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D201" t="s" s="2">
         <v>79</v>
@@ -26458,7 +26455,7 @@
         <v>79</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L201" t="s" s="2">
         <v>414</v>
@@ -26549,13 +26546,13 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B202" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D202" t="s" s="2">
         <v>79</v>
@@ -26577,7 +26574,7 @@
         <v>79</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L202" t="s" s="2">
         <v>414</v>
@@ -26668,7 +26665,7 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B203" t="s" s="2">
         <v>420</v>
@@ -26787,7 +26784,7 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B204" t="s" s="2">
         <v>428</v>
@@ -26904,13 +26901,13 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D205" t="s" s="2">
         <v>79</v>
@@ -27021,7 +27018,7 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>367</v>
@@ -27136,7 +27133,7 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B207" t="s" s="2">
         <v>368</v>
@@ -27253,7 +27250,7 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B208" t="s" s="2">
         <v>369</v>
@@ -27372,7 +27369,7 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B209" t="s" s="2">
         <v>370</v>
@@ -27491,7 +27488,7 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B210" t="s" s="2">
         <v>376</v>
@@ -27539,7 +27536,7 @@
         <v>79</v>
       </c>
       <c r="S210" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="T210" t="s" s="2">
         <v>79</v>
@@ -27610,7 +27607,7 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B211" t="s" s="2">
         <v>383</v>
@@ -27727,7 +27724,7 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B212" t="s" s="2">
         <v>386</v>
@@ -27844,7 +27841,7 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B213" t="s" s="2">
         <v>391</v>
@@ -27961,7 +27958,7 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B214" t="s" s="2">
         <v>397</v>
@@ -28080,7 +28077,7 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B215" t="s" s="2">
         <v>405</v>
@@ -28199,7 +28196,7 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B216" t="s" s="2">
         <v>413</v>
@@ -28225,7 +28222,7 @@
         <v>79</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="L216" t="s" s="2">
         <v>414</v>
@@ -28276,10 +28273,10 @@
       </c>
       <c r="AC216" s="2"/>
       <c r="AD216" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE216" t="s" s="2">
-        <v>449</v>
+        <v>363</v>
       </c>
       <c r="AF216" t="s" s="2">
         <v>413</v>
@@ -28314,13 +28311,13 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B217" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D217" t="s" s="2">
         <v>79</v>
@@ -28342,7 +28339,7 @@
         <v>79</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L217" t="s" s="2">
         <v>414</v>
@@ -28433,13 +28430,13 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B218" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D218" t="s" s="2">
         <v>79</v>
@@ -28461,7 +28458,7 @@
         <v>79</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="L218" t="s" s="2">
         <v>414</v>
@@ -28552,13 +28549,13 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B219" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D219" t="s" s="2">
         <v>79</v>
@@ -28580,7 +28577,7 @@
         <v>79</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L219" t="s" s="2">
         <v>414</v>
@@ -28671,7 +28668,7 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B220" t="s" s="2">
         <v>420</v>
@@ -28790,7 +28787,7 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B221" t="s" s="2">
         <v>428</v>
@@ -28907,13 +28904,13 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B222" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D222" t="s" s="2">
         <v>79</v>
@@ -29024,7 +29021,7 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B223" t="s" s="2">
         <v>367</v>
@@ -29139,7 +29136,7 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B224" t="s" s="2">
         <v>368</v>
@@ -29256,7 +29253,7 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B225" t="s" s="2">
         <v>369</v>
@@ -29375,7 +29372,7 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B226" t="s" s="2">
         <v>370</v>
@@ -29494,7 +29491,7 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B227" t="s" s="2">
         <v>376</v>
@@ -29542,7 +29539,7 @@
         <v>79</v>
       </c>
       <c r="S227" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="T227" t="s" s="2">
         <v>79</v>
@@ -29613,7 +29610,7 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B228" t="s" s="2">
         <v>383</v>
@@ -29730,7 +29727,7 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B229" t="s" s="2">
         <v>386</v>
@@ -29847,7 +29844,7 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B230" t="s" s="2">
         <v>391</v>
@@ -29964,7 +29961,7 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B231" t="s" s="2">
         <v>397</v>
@@ -30083,7 +30080,7 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B232" t="s" s="2">
         <v>405</v>
@@ -30202,7 +30199,7 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B233" t="s" s="2">
         <v>413</v>
@@ -30228,7 +30225,7 @@
         <v>79</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="L233" t="s" s="2">
         <v>414</v>
@@ -30279,10 +30276,10 @@
       </c>
       <c r="AC233" s="2"/>
       <c r="AD233" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE233" t="s" s="2">
-        <v>449</v>
+        <v>363</v>
       </c>
       <c r="AF233" t="s" s="2">
         <v>413</v>
@@ -30317,13 +30314,13 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B234" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D234" t="s" s="2">
         <v>79</v>
@@ -30345,7 +30342,7 @@
         <v>79</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="L234" t="s" s="2">
         <v>414</v>
@@ -30436,13 +30433,13 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B235" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D235" t="s" s="2">
         <v>79</v>
@@ -30464,7 +30461,7 @@
         <v>79</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L235" t="s" s="2">
         <v>414</v>
@@ -30555,7 +30552,7 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B236" t="s" s="2">
         <v>420</v>
@@ -30674,7 +30671,7 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B237" t="s" s="2">
         <v>428</v>
@@ -30791,13 +30788,13 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B238" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D238" t="s" s="2">
         <v>79</v>
@@ -30908,7 +30905,7 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B239" t="s" s="2">
         <v>367</v>
@@ -31023,7 +31020,7 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B240" t="s" s="2">
         <v>368</v>
@@ -31140,7 +31137,7 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B241" t="s" s="2">
         <v>369</v>
@@ -31259,7 +31256,7 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B242" t="s" s="2">
         <v>370</v>
@@ -31378,7 +31375,7 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B243" t="s" s="2">
         <v>376</v>
@@ -31426,7 +31423,7 @@
         <v>79</v>
       </c>
       <c r="S243" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="T243" t="s" s="2">
         <v>79</v>
@@ -31497,7 +31494,7 @@
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B244" t="s" s="2">
         <v>383</v>
@@ -31614,7 +31611,7 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B245" t="s" s="2">
         <v>386</v>
@@ -31731,7 +31728,7 @@
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B246" t="s" s="2">
         <v>391</v>
@@ -31848,7 +31845,7 @@
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B247" t="s" s="2">
         <v>397</v>
@@ -31967,7 +31964,7 @@
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B248" t="s" s="2">
         <v>405</v>
@@ -32086,7 +32083,7 @@
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B249" t="s" s="2">
         <v>413</v>
@@ -32112,7 +32109,7 @@
         <v>79</v>
       </c>
       <c r="K249" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L249" t="s" s="2">
         <v>414</v>
@@ -32163,7 +32160,7 @@
       </c>
       <c r="AC249" s="2"/>
       <c r="AD249" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE249" t="s" s="2">
         <v>363</v>
@@ -32201,13 +32198,13 @@
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B250" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C250" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D250" t="s" s="2">
         <v>79</v>
@@ -32229,7 +32226,7 @@
         <v>79</v>
       </c>
       <c r="K250" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="L250" t="s" s="2">
         <v>414</v>
@@ -32320,13 +32317,13 @@
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B251" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C251" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D251" t="s" s="2">
         <v>79</v>
@@ -32348,7 +32345,7 @@
         <v>79</v>
       </c>
       <c r="K251" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="L251" t="s" s="2">
         <v>414</v>
@@ -32439,13 +32436,13 @@
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B252" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C252" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D252" t="s" s="2">
         <v>79</v>
@@ -32467,7 +32464,7 @@
         <v>79</v>
       </c>
       <c r="K252" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L252" t="s" s="2">
         <v>414</v>
@@ -32558,7 +32555,7 @@
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B253" t="s" s="2">
         <v>420</v>
@@ -32677,7 +32674,7 @@
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B254" t="s" s="2">
         <v>428</v>
@@ -32794,13 +32791,13 @@
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B255" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D255" t="s" s="2">
         <v>79</v>
@@ -32911,7 +32908,7 @@
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B256" t="s" s="2">
         <v>367</v>
@@ -33026,7 +33023,7 @@
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B257" t="s" s="2">
         <v>368</v>
@@ -33143,7 +33140,7 @@
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B258" t="s" s="2">
         <v>369</v>
@@ -33262,7 +33259,7 @@
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B259" t="s" s="2">
         <v>370</v>
@@ -33381,7 +33378,7 @@
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B260" t="s" s="2">
         <v>376</v>
@@ -33429,7 +33426,7 @@
         <v>79</v>
       </c>
       <c r="S260" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="T260" t="s" s="2">
         <v>79</v>
@@ -33500,7 +33497,7 @@
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B261" t="s" s="2">
         <v>383</v>
@@ -33617,7 +33614,7 @@
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B262" t="s" s="2">
         <v>386</v>
@@ -33734,7 +33731,7 @@
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B263" t="s" s="2">
         <v>391</v>
@@ -33851,7 +33848,7 @@
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B264" t="s" s="2">
         <v>397</v>
@@ -33970,7 +33967,7 @@
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B265" t="s" s="2">
         <v>405</v>
@@ -34089,7 +34086,7 @@
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B266" t="s" s="2">
         <v>413</v>
@@ -34115,7 +34112,7 @@
         <v>79</v>
       </c>
       <c r="K266" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="L266" t="s" s="2">
         <v>414</v>
@@ -34166,10 +34163,10 @@
       </c>
       <c r="AC266" s="2"/>
       <c r="AD266" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE266" t="s" s="2">
-        <v>449</v>
+        <v>363</v>
       </c>
       <c r="AF266" t="s" s="2">
         <v>413</v>
@@ -34204,13 +34201,13 @@
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B267" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C267" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D267" t="s" s="2">
         <v>79</v>
@@ -34232,7 +34229,7 @@
         <v>79</v>
       </c>
       <c r="K267" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="L267" t="s" s="2">
         <v>414</v>
@@ -34323,13 +34320,13 @@
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B268" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C268" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D268" t="s" s="2">
         <v>79</v>
@@ -34351,7 +34348,7 @@
         <v>79</v>
       </c>
       <c r="K268" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="L268" t="s" s="2">
         <v>414</v>
@@ -34442,13 +34439,13 @@
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B269" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C269" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D269" t="s" s="2">
         <v>79</v>
@@ -34470,7 +34467,7 @@
         <v>79</v>
       </c>
       <c r="K269" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L269" t="s" s="2">
         <v>414</v>
@@ -34561,7 +34558,7 @@
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B270" t="s" s="2">
         <v>420</v>
@@ -34680,7 +34677,7 @@
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B271" t="s" s="2">
         <v>428</v>
@@ -34797,13 +34794,13 @@
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B272" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C272" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D272" t="s" s="2">
         <v>79</v>
@@ -34914,7 +34911,7 @@
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B273" t="s" s="2">
         <v>367</v>
@@ -35029,7 +35026,7 @@
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B274" t="s" s="2">
         <v>368</v>
@@ -35146,7 +35143,7 @@
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B275" t="s" s="2">
         <v>369</v>
@@ -35265,7 +35262,7 @@
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B276" t="s" s="2">
         <v>370</v>
@@ -35384,7 +35381,7 @@
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B277" t="s" s="2">
         <v>376</v>
@@ -35432,7 +35429,7 @@
         <v>79</v>
       </c>
       <c r="S277" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="T277" t="s" s="2">
         <v>79</v>
@@ -35503,7 +35500,7 @@
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B278" t="s" s="2">
         <v>383</v>
@@ -35620,7 +35617,7 @@
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B279" t="s" s="2">
         <v>386</v>
@@ -35737,7 +35734,7 @@
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B280" t="s" s="2">
         <v>391</v>
@@ -35854,7 +35851,7 @@
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B281" t="s" s="2">
         <v>397</v>
@@ -35973,7 +35970,7 @@
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B282" t="s" s="2">
         <v>405</v>
@@ -36092,7 +36089,7 @@
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B283" t="s" s="2">
         <v>413</v>
@@ -36118,7 +36115,7 @@
         <v>79</v>
       </c>
       <c r="K283" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="L283" t="s" s="2">
         <v>414</v>
@@ -36169,10 +36166,10 @@
       </c>
       <c r="AC283" s="2"/>
       <c r="AD283" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE283" t="s" s="2">
-        <v>449</v>
+        <v>363</v>
       </c>
       <c r="AF283" t="s" s="2">
         <v>413</v>
@@ -36207,13 +36204,13 @@
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B284" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C284" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D284" t="s" s="2">
         <v>79</v>
@@ -36235,7 +36232,7 @@
         <v>79</v>
       </c>
       <c r="K284" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="L284" t="s" s="2">
         <v>414</v>
@@ -36326,13 +36323,13 @@
     </row>
     <row r="285">
       <c r="A285" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B285" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C285" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D285" t="s" s="2">
         <v>79</v>
@@ -36354,7 +36351,7 @@
         <v>79</v>
       </c>
       <c r="K285" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L285" t="s" s="2">
         <v>414</v>
@@ -36445,7 +36442,7 @@
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B286" t="s" s="2">
         <v>420</v>
@@ -36564,7 +36561,7 @@
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B287" t="s" s="2">
         <v>428</v>
@@ -36681,13 +36678,13 @@
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B288" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C288" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D288" t="s" s="2">
         <v>79</v>
@@ -36798,7 +36795,7 @@
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B289" t="s" s="2">
         <v>367</v>
@@ -36913,7 +36910,7 @@
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B290" t="s" s="2">
         <v>368</v>
@@ -37030,7 +37027,7 @@
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B291" t="s" s="2">
         <v>369</v>
@@ -37149,7 +37146,7 @@
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B292" t="s" s="2">
         <v>370</v>
@@ -37268,7 +37265,7 @@
     </row>
     <row r="293">
       <c r="A293" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B293" t="s" s="2">
         <v>376</v>
@@ -37316,7 +37313,7 @@
         <v>79</v>
       </c>
       <c r="S293" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="T293" t="s" s="2">
         <v>79</v>
@@ -37387,7 +37384,7 @@
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B294" t="s" s="2">
         <v>383</v>
@@ -37504,7 +37501,7 @@
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B295" t="s" s="2">
         <v>386</v>
@@ -37621,7 +37618,7 @@
     </row>
     <row r="296">
       <c r="A296" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B296" t="s" s="2">
         <v>391</v>
@@ -37738,7 +37735,7 @@
     </row>
     <row r="297">
       <c r="A297" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B297" t="s" s="2">
         <v>397</v>
@@ -37857,7 +37854,7 @@
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B298" t="s" s="2">
         <v>405</v>
@@ -37976,7 +37973,7 @@
     </row>
     <row r="299">
       <c r="A299" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B299" t="s" s="2">
         <v>413</v>
@@ -38002,7 +37999,7 @@
         <v>79</v>
       </c>
       <c r="K299" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="L299" t="s" s="2">
         <v>414</v>
@@ -38053,10 +38050,10 @@
       </c>
       <c r="AC299" s="2"/>
       <c r="AD299" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="AE299" t="s" s="2">
-        <v>449</v>
+        <v>363</v>
       </c>
       <c r="AF299" t="s" s="2">
         <v>413</v>
@@ -38091,13 +38088,13 @@
     </row>
     <row r="300">
       <c r="A300" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B300" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C300" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D300" t="s" s="2">
         <v>79</v>
@@ -38119,7 +38116,7 @@
         <v>79</v>
       </c>
       <c r="K300" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L300" t="s" s="2">
         <v>414</v>
@@ -38210,13 +38207,13 @@
     </row>
     <row r="301">
       <c r="A301" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B301" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D301" t="s" s="2">
         <v>79</v>
@@ -38238,7 +38235,7 @@
         <v>79</v>
       </c>
       <c r="K301" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L301" t="s" s="2">
         <v>414</v>
@@ -38329,7 +38326,7 @@
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B302" t="s" s="2">
         <v>420</v>
@@ -38448,7 +38445,7 @@
     </row>
     <row r="303">
       <c r="A303" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B303" t="s" s="2">
         <v>428</v>
@@ -38565,13 +38562,13 @@
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B304" t="s" s="2">
         <v>358</v>
       </c>
       <c r="C304" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D304" t="s" s="2">
         <v>79</v>
@@ -38682,7 +38679,7 @@
     </row>
     <row r="305">
       <c r="A305" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B305" t="s" s="2">
         <v>367</v>
@@ -38797,7 +38794,7 @@
     </row>
     <row r="306">
       <c r="A306" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B306" t="s" s="2">
         <v>368</v>
@@ -38914,7 +38911,7 @@
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B307" t="s" s="2">
         <v>369</v>
@@ -39033,7 +39030,7 @@
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B308" t="s" s="2">
         <v>370</v>
@@ -39152,7 +39149,7 @@
     </row>
     <row r="309">
       <c r="A309" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B309" t="s" s="2">
         <v>376</v>
@@ -39200,7 +39197,7 @@
         <v>79</v>
       </c>
       <c r="S309" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="T309" t="s" s="2">
         <v>79</v>
@@ -39271,7 +39268,7 @@
     </row>
     <row r="310">
       <c r="A310" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B310" t="s" s="2">
         <v>383</v>
@@ -39388,7 +39385,7 @@
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B311" t="s" s="2">
         <v>386</v>
@@ -39505,7 +39502,7 @@
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B312" t="s" s="2">
         <v>391</v>
@@ -39622,7 +39619,7 @@
     </row>
     <row r="313">
       <c r="A313" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B313" t="s" s="2">
         <v>397</v>
@@ -39741,7 +39738,7 @@
     </row>
     <row r="314">
       <c r="A314" t="s" s="2">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B314" t="s" s="2">
         <v>405</v>
@@ -39860,7 +39857,7 @@
     </row>
     <row r="315">
       <c r="A315" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B315" t="s" s="2">
         <v>413</v>
@@ -39977,7 +39974,7 @@
     </row>
     <row r="316">
       <c r="A316" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B316" t="s" s="2">
         <v>420</v>
@@ -40096,7 +40093,7 @@
     </row>
     <row r="317">
       <c r="A317" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B317" t="s" s="2">
         <v>428</v>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T06:33:09+00:00</t>
+    <t>2026-02-03T10:06:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11883" uniqueCount="789">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11921" uniqueCount="792">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-03T10:06:44+00:00</t>
+    <t>2026-02-03T10:34:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -717,7 +717,7 @@
     <t>Composition.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Device|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-device|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|RelatedPerson|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization)
 </t>
   </si>
   <si>
@@ -930,7 +930,7 @@
     <t>Composition.custodian</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization)
 </t>
   </si>
   <si>
@@ -1016,7 +1016,7 @@
   </si>
   <si>
     <t>Identifier
-Reference(Composition|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-composition)</t>
+Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-composition)</t>
   </si>
   <si>
     <t>Target of the relationship</t>
@@ -2165,7 +2165,7 @@
     <t>Composition.section:sectionPlanOfCare.entry</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-careplan|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-documentreference)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-careplan|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-immunizationrecommendation|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-documentreference)
 </t>
   </si>
   <si>
@@ -2176,6 +2176,16 @@
   </si>
   <si>
     <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-careplan)
+</t>
+  </si>
+  <si>
+    <t>Composition.section:sectionPlanOfCare.entry:immunizationRecommendation</t>
+  </si>
+  <si>
+    <t>immunizationRecommendation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-immunizationrecommendation)
 </t>
   </si>
   <si>
@@ -2844,7 +2854,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO317"/>
+  <dimension ref="A1:AO318"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="65.23828125" customWidth="true" bestFit="true"/>
@@ -30439,7 +30449,7 @@
         <v>413</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>462</v>
+        <v>682</v>
       </c>
       <c r="D235" t="s" s="2">
         <v>79</v>
@@ -30461,7 +30471,7 @@
         <v>79</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>463</v>
+        <v>683</v>
       </c>
       <c r="L235" t="s" s="2">
         <v>414</v>
@@ -30552,12 +30562,14 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="C236" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="C236" t="s" s="2">
+        <v>462</v>
+      </c>
       <c r="D236" t="s" s="2">
         <v>79</v>
       </c>
@@ -30566,7 +30578,7 @@
         <v>80</v>
       </c>
       <c r="G236" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H236" t="s" s="2">
         <v>79</v>
@@ -30578,20 +30590,18 @@
         <v>79</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>172</v>
+        <v>463</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="N236" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O236" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="O236" s="2"/>
       <c r="P236" t="s" s="2">
         <v>79</v>
       </c>
@@ -30615,13 +30625,13 @@
         <v>79</v>
       </c>
       <c r="X236" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="Y236" t="s" s="2">
-        <v>425</v>
+        <v>79</v>
       </c>
       <c r="Z236" t="s" s="2">
-        <v>426</v>
+        <v>79</v>
       </c>
       <c r="AA236" t="s" s="2">
         <v>79</v>
@@ -30639,13 +30649,13 @@
         <v>79</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH236" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI236" t="s" s="2">
         <v>417</v>
@@ -30657,10 +30667,10 @@
         <v>79</v>
       </c>
       <c r="AL236" t="s" s="2">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="AM236" t="s" s="2">
-        <v>168</v>
+        <v>419</v>
       </c>
       <c r="AN236" t="s" s="2">
         <v>79</v>
@@ -30671,10 +30681,10 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -30685,7 +30695,7 @@
         <v>80</v>
       </c>
       <c r="G237" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H237" t="s" s="2">
         <v>79</v>
@@ -30697,18 +30707,20 @@
         <v>79</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="N237" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O237" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="O237" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P237" t="s" s="2">
         <v>79</v>
       </c>
@@ -30732,13 +30744,13 @@
         <v>79</v>
       </c>
       <c r="X237" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="Y237" t="s" s="2">
-        <v>79</v>
+        <v>425</v>
       </c>
       <c r="Z237" t="s" s="2">
-        <v>79</v>
+        <v>426</v>
       </c>
       <c r="AA237" t="s" s="2">
         <v>79</v>
@@ -30756,16 +30768,16 @@
         <v>79</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH237" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI237" t="s" s="2">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="AJ237" t="s" s="2">
         <v>103</v>
@@ -30774,10 +30786,10 @@
         <v>79</v>
       </c>
       <c r="AL237" t="s" s="2">
-        <v>365</v>
+        <v>427</v>
       </c>
       <c r="AM237" t="s" s="2">
-        <v>432</v>
+        <v>168</v>
       </c>
       <c r="AN237" t="s" s="2">
         <v>79</v>
@@ -30788,14 +30800,12 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="C238" t="s" s="2">
-        <v>685</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
         <v>79</v>
       </c>
@@ -30804,7 +30814,7 @@
         <v>80</v>
       </c>
       <c r="G238" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H238" t="s" s="2">
         <v>79</v>
@@ -30816,15 +30826,17 @@
         <v>79</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>360</v>
+        <v>429</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N238" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="N238" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="O238" s="2"/>
       <c r="P238" t="s" s="2">
         <v>79</v>
@@ -30873,7 +30885,7 @@
         <v>79</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>358</v>
+        <v>428</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>80</v>
@@ -30882,10 +30894,10 @@
         <v>81</v>
       </c>
       <c r="AI238" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="AJ238" t="s" s="2">
-        <v>364</v>
+        <v>103</v>
       </c>
       <c r="AK238" t="s" s="2">
         <v>79</v>
@@ -30894,7 +30906,7 @@
         <v>365</v>
       </c>
       <c r="AM238" t="s" s="2">
-        <v>366</v>
+        <v>432</v>
       </c>
       <c r="AN238" t="s" s="2">
         <v>79</v>
@@ -30905,12 +30917,14 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C239" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="C239" t="s" s="2">
+        <v>688</v>
+      </c>
       <c r="D239" t="s" s="2">
         <v>79</v>
       </c>
@@ -30931,13 +30945,13 @@
         <v>79</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>262</v>
+        <v>360</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>263</v>
+        <v>361</v>
       </c>
       <c r="N239" s="2"/>
       <c r="O239" s="2"/>
@@ -30988,28 +31002,28 @@
         <v>79</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>264</v>
+        <v>358</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH239" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI239" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ239" t="s" s="2">
-        <v>79</v>
+        <v>364</v>
       </c>
       <c r="AK239" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL239" t="s" s="2">
-        <v>168</v>
+        <v>365</v>
       </c>
       <c r="AM239" t="s" s="2">
-        <v>79</v>
+        <v>366</v>
       </c>
       <c r="AN239" t="s" s="2">
         <v>79</v>
@@ -31020,21 +31034,21 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E240" s="2"/>
       <c r="F240" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G240" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H240" t="s" s="2">
         <v>79</v>
@@ -31046,17 +31060,15 @@
         <v>79</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>137</v>
+        <v>237</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>138</v>
+        <v>262</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N240" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N240" s="2"/>
       <c r="O240" s="2"/>
       <c r="P240" t="s" s="2">
         <v>79</v>
@@ -31105,19 +31117,19 @@
         <v>79</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH240" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI240" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ240" t="s" s="2">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="AK240" t="s" s="2">
         <v>79</v>
@@ -31137,14 +31149,14 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
-        <v>269</v>
+        <v>136</v>
       </c>
       <c r="E241" s="2"/>
       <c r="F241" t="s" s="2">
@@ -31157,26 +31169,24 @@
         <v>79</v>
       </c>
       <c r="I241" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J241" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K241" t="s" s="2">
         <v>137</v>
       </c>
       <c r="L241" t="s" s="2">
-        <v>270</v>
+        <v>138</v>
       </c>
       <c r="M241" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="N241" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="O241" t="s" s="2">
-        <v>146</v>
-      </c>
+      <c r="O241" s="2"/>
       <c r="P241" t="s" s="2">
         <v>79</v>
       </c>
@@ -31224,7 +31234,7 @@
         <v>79</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>80</v>
@@ -31242,7 +31252,7 @@
         <v>79</v>
       </c>
       <c r="AL241" t="s" s="2">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="AM241" t="s" s="2">
         <v>79</v>
@@ -31256,45 +31266,45 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
-        <v>371</v>
+        <v>269</v>
       </c>
       <c r="E242" s="2"/>
       <c r="F242" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G242" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H242" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I242" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J242" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K242" t="s" s="2">
-        <v>237</v>
+        <v>137</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>372</v>
+        <v>270</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>373</v>
+        <v>271</v>
       </c>
       <c r="N242" t="s" s="2">
-        <v>374</v>
+        <v>140</v>
       </c>
       <c r="O242" t="s" s="2">
-        <v>375</v>
+        <v>146</v>
       </c>
       <c r="P242" t="s" s="2">
         <v>79</v>
@@ -31343,28 +31353,28 @@
         <v>79</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>370</v>
+        <v>272</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH242" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI242" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ242" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK242" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL242" t="s" s="2">
-        <v>241</v>
+        <v>134</v>
       </c>
       <c r="AM242" t="s" s="2">
-        <v>242</v>
+        <v>79</v>
       </c>
       <c r="AN242" t="s" s="2">
         <v>79</v>
@@ -31375,18 +31385,18 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
-        <v>79</v>
+        <v>371</v>
       </c>
       <c r="E243" s="2"/>
       <c r="F243" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G243" t="s" s="2">
         <v>91</v>
@@ -31401,19 +31411,19 @@
         <v>79</v>
       </c>
       <c r="K243" t="s" s="2">
-        <v>172</v>
+        <v>237</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="N243" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="O243" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="P243" t="s" s="2">
         <v>79</v>
@@ -31423,7 +31433,7 @@
         <v>79</v>
       </c>
       <c r="S243" t="s" s="2">
-        <v>691</v>
+        <v>79</v>
       </c>
       <c r="T243" t="s" s="2">
         <v>79</v>
@@ -31438,13 +31448,13 @@
         <v>79</v>
       </c>
       <c r="X243" t="s" s="2">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="Y243" t="s" s="2">
-        <v>381</v>
+        <v>79</v>
       </c>
       <c r="Z243" t="s" s="2">
-        <v>382</v>
+        <v>79</v>
       </c>
       <c r="AA243" t="s" s="2">
         <v>79</v>
@@ -31462,7 +31472,7 @@
         <v>79</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>80</v>
@@ -31480,10 +31490,10 @@
         <v>79</v>
       </c>
       <c r="AL243" t="s" s="2">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="AM243" t="s" s="2">
-        <v>181</v>
+        <v>242</v>
       </c>
       <c r="AN243" t="s" s="2">
         <v>79</v>
@@ -31494,10 +31504,10 @@
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -31505,10 +31515,10 @@
       </c>
       <c r="E244" s="2"/>
       <c r="F244" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G244" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H244" t="s" s="2">
         <v>79</v>
@@ -31520,17 +31530,19 @@
         <v>79</v>
       </c>
       <c r="K244" t="s" s="2">
-        <v>227</v>
+        <v>172</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="M244" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N244" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N244" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="O244" t="s" s="2">
-        <v>230</v>
+        <v>380</v>
       </c>
       <c r="P244" t="s" s="2">
         <v>79</v>
@@ -31540,7 +31552,7 @@
         <v>79</v>
       </c>
       <c r="S244" t="s" s="2">
-        <v>79</v>
+        <v>694</v>
       </c>
       <c r="T244" t="s" s="2">
         <v>79</v>
@@ -31555,13 +31567,13 @@
         <v>79</v>
       </c>
       <c r="X244" t="s" s="2">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="Y244" t="s" s="2">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="Z244" t="s" s="2">
-        <v>79</v>
+        <v>382</v>
       </c>
       <c r="AA244" t="s" s="2">
         <v>79</v>
@@ -31579,13 +31591,13 @@
         <v>79</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH244" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI244" t="s" s="2">
         <v>79</v>
@@ -31597,24 +31609,24 @@
         <v>79</v>
       </c>
       <c r="AL244" t="s" s="2">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="AM244" t="s" s="2">
-        <v>233</v>
+        <v>181</v>
       </c>
       <c r="AN244" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO244" t="s" s="2">
-        <v>235</v>
+        <v>79</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -31625,7 +31637,7 @@
         <v>80</v>
       </c>
       <c r="G245" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H245" t="s" s="2">
         <v>79</v>
@@ -31637,18 +31649,18 @@
         <v>79</v>
       </c>
       <c r="K245" t="s" s="2">
-        <v>354</v>
+        <v>227</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="M245" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N245" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O245" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N245" s="2"/>
+      <c r="O245" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P245" t="s" s="2">
         <v>79</v>
       </c>
@@ -31696,13 +31708,13 @@
         <v>79</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH245" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI245" t="s" s="2">
         <v>79</v>
@@ -31714,24 +31726,24 @@
         <v>79</v>
       </c>
       <c r="AL245" t="s" s="2">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="AM245" t="s" s="2">
-        <v>390</v>
+        <v>233</v>
       </c>
       <c r="AN245" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO245" t="s" s="2">
-        <v>79</v>
+        <v>235</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -31754,16 +31766,16 @@
         <v>79</v>
       </c>
       <c r="K246" t="s" s="2">
-        <v>121</v>
+        <v>354</v>
       </c>
       <c r="L246" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="N246" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="O246" s="2"/>
       <c r="P246" t="s" s="2">
@@ -31813,7 +31825,7 @@
         <v>79</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>80</v>
@@ -31822,7 +31834,7 @@
         <v>91</v>
       </c>
       <c r="AI246" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="AJ246" t="s" s="2">
         <v>103</v>
@@ -31831,10 +31843,10 @@
         <v>79</v>
       </c>
       <c r="AL246" t="s" s="2">
-        <v>396</v>
+        <v>79</v>
       </c>
       <c r="AM246" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="AN246" t="s" s="2">
         <v>79</v>
@@ -31845,10 +31857,10 @@
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -31871,20 +31883,18 @@
         <v>79</v>
       </c>
       <c r="K247" t="s" s="2">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="L247" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="N247" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O247" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="O247" s="2"/>
       <c r="P247" t="s" s="2">
         <v>79</v>
       </c>
@@ -31908,13 +31918,13 @@
         <v>79</v>
       </c>
       <c r="X247" t="s" s="2">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="Y247" t="s" s="2">
-        <v>402</v>
+        <v>79</v>
       </c>
       <c r="Z247" t="s" s="2">
-        <v>403</v>
+        <v>79</v>
       </c>
       <c r="AA247" t="s" s="2">
         <v>79</v>
@@ -31932,7 +31942,7 @@
         <v>79</v>
       </c>
       <c r="AF247" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="AG247" t="s" s="2">
         <v>80</v>
@@ -31941,7 +31951,7 @@
         <v>91</v>
       </c>
       <c r="AI247" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="AJ247" t="s" s="2">
         <v>103</v>
@@ -31950,24 +31960,24 @@
         <v>79</v>
       </c>
       <c r="AL247" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="AM247" t="s" s="2">
-        <v>168</v>
+        <v>396</v>
       </c>
       <c r="AN247" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO247" t="s" s="2">
-        <v>183</v>
+        <v>79</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -31990,19 +32000,19 @@
         <v>79</v>
       </c>
       <c r="K248" t="s" s="2">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="L248" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="M248" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="N248" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="O248" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="P248" t="s" s="2">
         <v>79</v>
@@ -32027,13 +32037,13 @@
         <v>79</v>
       </c>
       <c r="X248" t="s" s="2">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="Y248" t="s" s="2">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="Z248" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="AA248" t="s" s="2">
         <v>79</v>
@@ -32051,7 +32061,7 @@
         <v>79</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="AG248" t="s" s="2">
         <v>80</v>
@@ -32069,7 +32079,7 @@
         <v>79</v>
       </c>
       <c r="AL248" t="s" s="2">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="AM248" t="s" s="2">
         <v>168</v>
@@ -32078,15 +32088,15 @@
         <v>79</v>
       </c>
       <c r="AO248" t="s" s="2">
-        <v>79</v>
+        <v>183</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -32097,7 +32107,7 @@
         <v>80</v>
       </c>
       <c r="G249" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H249" t="s" s="2">
         <v>79</v>
@@ -32109,18 +32119,20 @@
         <v>79</v>
       </c>
       <c r="K249" t="s" s="2">
-        <v>614</v>
+        <v>172</v>
       </c>
       <c r="L249" t="s" s="2">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="M249" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="N249" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O249" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="O249" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P249" t="s" s="2">
         <v>79</v>
       </c>
@@ -32144,38 +32156,40 @@
         <v>79</v>
       </c>
       <c r="X249" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="Y249" t="s" s="2">
-        <v>79</v>
+        <v>410</v>
       </c>
       <c r="Z249" t="s" s="2">
-        <v>79</v>
+        <v>411</v>
       </c>
       <c r="AA249" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB249" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AC249" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC249" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD249" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE249" t="s" s="2">
-        <v>363</v>
+        <v>79</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH249" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI249" t="s" s="2">
-        <v>417</v>
+        <v>79</v>
       </c>
       <c r="AJ249" t="s" s="2">
         <v>103</v>
@@ -32184,10 +32198,10 @@
         <v>79</v>
       </c>
       <c r="AL249" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="AM249" t="s" s="2">
-        <v>419</v>
+        <v>168</v>
       </c>
       <c r="AN249" t="s" s="2">
         <v>79</v>
@@ -32198,14 +32212,12 @@
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B250" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="C250" t="s" s="2">
-        <v>699</v>
-      </c>
+      <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
         <v>79</v>
       </c>
@@ -32214,7 +32226,7 @@
         <v>80</v>
       </c>
       <c r="G250" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H250" t="s" s="2">
         <v>79</v>
@@ -32226,7 +32238,7 @@
         <v>79</v>
       </c>
       <c r="K250" t="s" s="2">
-        <v>700</v>
+        <v>614</v>
       </c>
       <c r="L250" t="s" s="2">
         <v>414</v>
@@ -32273,16 +32285,14 @@
         <v>79</v>
       </c>
       <c r="AB250" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC250" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="AC250" s="2"/>
       <c r="AD250" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE250" t="s" s="2">
-        <v>79</v>
+        <v>363</v>
       </c>
       <c r="AF250" t="s" s="2">
         <v>413</v>
@@ -32442,7 +32452,7 @@
         <v>413</v>
       </c>
       <c r="C252" t="s" s="2">
-        <v>462</v>
+        <v>705</v>
       </c>
       <c r="D252" t="s" s="2">
         <v>79</v>
@@ -32452,7 +32462,7 @@
         <v>80</v>
       </c>
       <c r="G252" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H252" t="s" s="2">
         <v>79</v>
@@ -32464,7 +32474,7 @@
         <v>79</v>
       </c>
       <c r="K252" t="s" s="2">
-        <v>463</v>
+        <v>706</v>
       </c>
       <c r="L252" t="s" s="2">
         <v>414</v>
@@ -32555,12 +32565,14 @@
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="C253" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="C253" t="s" s="2">
+        <v>462</v>
+      </c>
       <c r="D253" t="s" s="2">
         <v>79</v>
       </c>
@@ -32569,7 +32581,7 @@
         <v>80</v>
       </c>
       <c r="G253" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H253" t="s" s="2">
         <v>79</v>
@@ -32581,20 +32593,18 @@
         <v>79</v>
       </c>
       <c r="K253" t="s" s="2">
-        <v>172</v>
+        <v>463</v>
       </c>
       <c r="L253" t="s" s="2">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="M253" t="s" s="2">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="N253" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O253" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="O253" s="2"/>
       <c r="P253" t="s" s="2">
         <v>79</v>
       </c>
@@ -32618,13 +32628,13 @@
         <v>79</v>
       </c>
       <c r="X253" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="Y253" t="s" s="2">
-        <v>425</v>
+        <v>79</v>
       </c>
       <c r="Z253" t="s" s="2">
-        <v>426</v>
+        <v>79</v>
       </c>
       <c r="AA253" t="s" s="2">
         <v>79</v>
@@ -32642,13 +32652,13 @@
         <v>79</v>
       </c>
       <c r="AF253" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="AG253" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH253" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI253" t="s" s="2">
         <v>417</v>
@@ -32660,10 +32670,10 @@
         <v>79</v>
       </c>
       <c r="AL253" t="s" s="2">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="AM253" t="s" s="2">
-        <v>168</v>
+        <v>419</v>
       </c>
       <c r="AN253" t="s" s="2">
         <v>79</v>
@@ -32674,10 +32684,10 @@
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -32688,7 +32698,7 @@
         <v>80</v>
       </c>
       <c r="G254" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H254" t="s" s="2">
         <v>79</v>
@@ -32700,18 +32710,20 @@
         <v>79</v>
       </c>
       <c r="K254" t="s" s="2">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="L254" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="M254" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="N254" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O254" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="O254" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P254" t="s" s="2">
         <v>79</v>
       </c>
@@ -32735,13 +32747,13 @@
         <v>79</v>
       </c>
       <c r="X254" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="Y254" t="s" s="2">
-        <v>79</v>
+        <v>425</v>
       </c>
       <c r="Z254" t="s" s="2">
-        <v>79</v>
+        <v>426</v>
       </c>
       <c r="AA254" t="s" s="2">
         <v>79</v>
@@ -32759,16 +32771,16 @@
         <v>79</v>
       </c>
       <c r="AF254" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="AG254" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH254" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI254" t="s" s="2">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="AJ254" t="s" s="2">
         <v>103</v>
@@ -32777,10 +32789,10 @@
         <v>79</v>
       </c>
       <c r="AL254" t="s" s="2">
-        <v>365</v>
+        <v>427</v>
       </c>
       <c r="AM254" t="s" s="2">
-        <v>432</v>
+        <v>168</v>
       </c>
       <c r="AN254" t="s" s="2">
         <v>79</v>
@@ -32791,14 +32803,12 @@
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="C255" t="s" s="2">
-        <v>708</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
         <v>79</v>
       </c>
@@ -32807,7 +32817,7 @@
         <v>80</v>
       </c>
       <c r="G255" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H255" t="s" s="2">
         <v>79</v>
@@ -32819,15 +32829,17 @@
         <v>79</v>
       </c>
       <c r="K255" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="L255" t="s" s="2">
-        <v>360</v>
+        <v>429</v>
       </c>
       <c r="M255" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N255" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="N255" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="O255" s="2"/>
       <c r="P255" t="s" s="2">
         <v>79</v>
@@ -32876,7 +32888,7 @@
         <v>79</v>
       </c>
       <c r="AF255" t="s" s="2">
-        <v>358</v>
+        <v>428</v>
       </c>
       <c r="AG255" t="s" s="2">
         <v>80</v>
@@ -32885,10 +32897,10 @@
         <v>81</v>
       </c>
       <c r="AI255" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="AJ255" t="s" s="2">
-        <v>364</v>
+        <v>103</v>
       </c>
       <c r="AK255" t="s" s="2">
         <v>79</v>
@@ -32897,7 +32909,7 @@
         <v>365</v>
       </c>
       <c r="AM255" t="s" s="2">
-        <v>366</v>
+        <v>432</v>
       </c>
       <c r="AN255" t="s" s="2">
         <v>79</v>
@@ -32908,12 +32920,14 @@
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C256" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="C256" t="s" s="2">
+        <v>711</v>
+      </c>
       <c r="D256" t="s" s="2">
         <v>79</v>
       </c>
@@ -32934,13 +32948,13 @@
         <v>79</v>
       </c>
       <c r="K256" t="s" s="2">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="L256" t="s" s="2">
-        <v>262</v>
+        <v>360</v>
       </c>
       <c r="M256" t="s" s="2">
-        <v>263</v>
+        <v>361</v>
       </c>
       <c r="N256" s="2"/>
       <c r="O256" s="2"/>
@@ -32991,28 +33005,28 @@
         <v>79</v>
       </c>
       <c r="AF256" t="s" s="2">
-        <v>264</v>
+        <v>358</v>
       </c>
       <c r="AG256" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH256" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI256" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ256" t="s" s="2">
-        <v>79</v>
+        <v>364</v>
       </c>
       <c r="AK256" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL256" t="s" s="2">
-        <v>168</v>
+        <v>365</v>
       </c>
       <c r="AM256" t="s" s="2">
-        <v>79</v>
+        <v>366</v>
       </c>
       <c r="AN256" t="s" s="2">
         <v>79</v>
@@ -33023,21 +33037,21 @@
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E257" s="2"/>
       <c r="F257" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G257" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H257" t="s" s="2">
         <v>79</v>
@@ -33049,17 +33063,15 @@
         <v>79</v>
       </c>
       <c r="K257" t="s" s="2">
-        <v>137</v>
+        <v>237</v>
       </c>
       <c r="L257" t="s" s="2">
-        <v>138</v>
+        <v>262</v>
       </c>
       <c r="M257" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N257" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N257" s="2"/>
       <c r="O257" s="2"/>
       <c r="P257" t="s" s="2">
         <v>79</v>
@@ -33108,19 +33120,19 @@
         <v>79</v>
       </c>
       <c r="AF257" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AG257" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH257" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI257" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ257" t="s" s="2">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="AK257" t="s" s="2">
         <v>79</v>
@@ -33140,14 +33152,14 @@
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
-        <v>269</v>
+        <v>136</v>
       </c>
       <c r="E258" s="2"/>
       <c r="F258" t="s" s="2">
@@ -33160,26 +33172,24 @@
         <v>79</v>
       </c>
       <c r="I258" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J258" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K258" t="s" s="2">
         <v>137</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>270</v>
+        <v>138</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="N258" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="O258" t="s" s="2">
-        <v>146</v>
-      </c>
+      <c r="O258" s="2"/>
       <c r="P258" t="s" s="2">
         <v>79</v>
       </c>
@@ -33227,7 +33237,7 @@
         <v>79</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>80</v>
@@ -33245,7 +33255,7 @@
         <v>79</v>
       </c>
       <c r="AL258" t="s" s="2">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="AM258" t="s" s="2">
         <v>79</v>
@@ -33259,45 +33269,45 @@
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
-        <v>371</v>
+        <v>269</v>
       </c>
       <c r="E259" s="2"/>
       <c r="F259" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G259" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H259" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I259" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J259" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K259" t="s" s="2">
-        <v>237</v>
+        <v>137</v>
       </c>
       <c r="L259" t="s" s="2">
-        <v>372</v>
+        <v>270</v>
       </c>
       <c r="M259" t="s" s="2">
-        <v>373</v>
+        <v>271</v>
       </c>
       <c r="N259" t="s" s="2">
-        <v>374</v>
+        <v>140</v>
       </c>
       <c r="O259" t="s" s="2">
-        <v>375</v>
+        <v>146</v>
       </c>
       <c r="P259" t="s" s="2">
         <v>79</v>
@@ -33346,28 +33356,28 @@
         <v>79</v>
       </c>
       <c r="AF259" t="s" s="2">
-        <v>370</v>
+        <v>272</v>
       </c>
       <c r="AG259" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH259" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI259" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ259" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK259" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL259" t="s" s="2">
-        <v>241</v>
+        <v>134</v>
       </c>
       <c r="AM259" t="s" s="2">
-        <v>242</v>
+        <v>79</v>
       </c>
       <c r="AN259" t="s" s="2">
         <v>79</v>
@@ -33378,18 +33388,18 @@
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
-        <v>79</v>
+        <v>371</v>
       </c>
       <c r="E260" s="2"/>
       <c r="F260" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G260" t="s" s="2">
         <v>91</v>
@@ -33404,19 +33414,19 @@
         <v>79</v>
       </c>
       <c r="K260" t="s" s="2">
-        <v>172</v>
+        <v>237</v>
       </c>
       <c r="L260" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="M260" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="N260" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="O260" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="P260" t="s" s="2">
         <v>79</v>
@@ -33426,7 +33436,7 @@
         <v>79</v>
       </c>
       <c r="S260" t="s" s="2">
-        <v>714</v>
+        <v>79</v>
       </c>
       <c r="T260" t="s" s="2">
         <v>79</v>
@@ -33441,13 +33451,13 @@
         <v>79</v>
       </c>
       <c r="X260" t="s" s="2">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="Y260" t="s" s="2">
-        <v>381</v>
+        <v>79</v>
       </c>
       <c r="Z260" t="s" s="2">
-        <v>382</v>
+        <v>79</v>
       </c>
       <c r="AA260" t="s" s="2">
         <v>79</v>
@@ -33465,7 +33475,7 @@
         <v>79</v>
       </c>
       <c r="AF260" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="AG260" t="s" s="2">
         <v>80</v>
@@ -33483,10 +33493,10 @@
         <v>79</v>
       </c>
       <c r="AL260" t="s" s="2">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="AM260" t="s" s="2">
-        <v>181</v>
+        <v>242</v>
       </c>
       <c r="AN260" t="s" s="2">
         <v>79</v>
@@ -33497,10 +33507,10 @@
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -33508,10 +33518,10 @@
       </c>
       <c r="E261" s="2"/>
       <c r="F261" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G261" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H261" t="s" s="2">
         <v>79</v>
@@ -33523,17 +33533,19 @@
         <v>79</v>
       </c>
       <c r="K261" t="s" s="2">
-        <v>227</v>
+        <v>172</v>
       </c>
       <c r="L261" t="s" s="2">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="M261" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N261" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N261" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="O261" t="s" s="2">
-        <v>230</v>
+        <v>380</v>
       </c>
       <c r="P261" t="s" s="2">
         <v>79</v>
@@ -33543,7 +33555,7 @@
         <v>79</v>
       </c>
       <c r="S261" t="s" s="2">
-        <v>79</v>
+        <v>717</v>
       </c>
       <c r="T261" t="s" s="2">
         <v>79</v>
@@ -33558,13 +33570,13 @@
         <v>79</v>
       </c>
       <c r="X261" t="s" s="2">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="Y261" t="s" s="2">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="Z261" t="s" s="2">
-        <v>79</v>
+        <v>382</v>
       </c>
       <c r="AA261" t="s" s="2">
         <v>79</v>
@@ -33582,13 +33594,13 @@
         <v>79</v>
       </c>
       <c r="AF261" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="AG261" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH261" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI261" t="s" s="2">
         <v>79</v>
@@ -33600,24 +33612,24 @@
         <v>79</v>
       </c>
       <c r="AL261" t="s" s="2">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="AM261" t="s" s="2">
-        <v>233</v>
+        <v>181</v>
       </c>
       <c r="AN261" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO261" t="s" s="2">
-        <v>235</v>
+        <v>79</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -33628,7 +33640,7 @@
         <v>80</v>
       </c>
       <c r="G262" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H262" t="s" s="2">
         <v>79</v>
@@ -33640,18 +33652,18 @@
         <v>79</v>
       </c>
       <c r="K262" t="s" s="2">
-        <v>354</v>
+        <v>227</v>
       </c>
       <c r="L262" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="M262" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N262" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O262" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N262" s="2"/>
+      <c r="O262" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P262" t="s" s="2">
         <v>79</v>
       </c>
@@ -33699,13 +33711,13 @@
         <v>79</v>
       </c>
       <c r="AF262" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AG262" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH262" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI262" t="s" s="2">
         <v>79</v>
@@ -33717,24 +33729,24 @@
         <v>79</v>
       </c>
       <c r="AL262" t="s" s="2">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="AM262" t="s" s="2">
-        <v>390</v>
+        <v>233</v>
       </c>
       <c r="AN262" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO262" t="s" s="2">
-        <v>79</v>
+        <v>235</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -33757,16 +33769,16 @@
         <v>79</v>
       </c>
       <c r="K263" t="s" s="2">
-        <v>121</v>
+        <v>354</v>
       </c>
       <c r="L263" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="M263" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="N263" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="O263" s="2"/>
       <c r="P263" t="s" s="2">
@@ -33816,7 +33828,7 @@
         <v>79</v>
       </c>
       <c r="AF263" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AG263" t="s" s="2">
         <v>80</v>
@@ -33825,7 +33837,7 @@
         <v>91</v>
       </c>
       <c r="AI263" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="AJ263" t="s" s="2">
         <v>103</v>
@@ -33834,10 +33846,10 @@
         <v>79</v>
       </c>
       <c r="AL263" t="s" s="2">
-        <v>396</v>
+        <v>79</v>
       </c>
       <c r="AM263" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="AN263" t="s" s="2">
         <v>79</v>
@@ -33848,10 +33860,10 @@
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
@@ -33874,20 +33886,18 @@
         <v>79</v>
       </c>
       <c r="K264" t="s" s="2">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="L264" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="M264" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="N264" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O264" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="O264" s="2"/>
       <c r="P264" t="s" s="2">
         <v>79</v>
       </c>
@@ -33911,13 +33921,13 @@
         <v>79</v>
       </c>
       <c r="X264" t="s" s="2">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="Y264" t="s" s="2">
-        <v>402</v>
+        <v>79</v>
       </c>
       <c r="Z264" t="s" s="2">
-        <v>403</v>
+        <v>79</v>
       </c>
       <c r="AA264" t="s" s="2">
         <v>79</v>
@@ -33935,7 +33945,7 @@
         <v>79</v>
       </c>
       <c r="AF264" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="AG264" t="s" s="2">
         <v>80</v>
@@ -33944,7 +33954,7 @@
         <v>91</v>
       </c>
       <c r="AI264" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="AJ264" t="s" s="2">
         <v>103</v>
@@ -33953,24 +33963,24 @@
         <v>79</v>
       </c>
       <c r="AL264" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="AM264" t="s" s="2">
-        <v>168</v>
+        <v>396</v>
       </c>
       <c r="AN264" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO264" t="s" s="2">
-        <v>183</v>
+        <v>79</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -33993,19 +34003,19 @@
         <v>79</v>
       </c>
       <c r="K265" t="s" s="2">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="L265" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="M265" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="N265" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="O265" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="P265" t="s" s="2">
         <v>79</v>
@@ -34030,13 +34040,13 @@
         <v>79</v>
       </c>
       <c r="X265" t="s" s="2">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="Y265" t="s" s="2">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="Z265" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="AA265" t="s" s="2">
         <v>79</v>
@@ -34054,7 +34064,7 @@
         <v>79</v>
       </c>
       <c r="AF265" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="AG265" t="s" s="2">
         <v>80</v>
@@ -34072,7 +34082,7 @@
         <v>79</v>
       </c>
       <c r="AL265" t="s" s="2">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="AM265" t="s" s="2">
         <v>168</v>
@@ -34081,15 +34091,15 @@
         <v>79</v>
       </c>
       <c r="AO265" t="s" s="2">
-        <v>79</v>
+        <v>183</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -34100,7 +34110,7 @@
         <v>80</v>
       </c>
       <c r="G266" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H266" t="s" s="2">
         <v>79</v>
@@ -34112,18 +34122,20 @@
         <v>79</v>
       </c>
       <c r="K266" t="s" s="2">
-        <v>721</v>
+        <v>172</v>
       </c>
       <c r="L266" t="s" s="2">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="M266" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="N266" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O266" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="O266" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P266" t="s" s="2">
         <v>79</v>
       </c>
@@ -34147,38 +34159,40 @@
         <v>79</v>
       </c>
       <c r="X266" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="Y266" t="s" s="2">
-        <v>79</v>
+        <v>410</v>
       </c>
       <c r="Z266" t="s" s="2">
-        <v>79</v>
+        <v>411</v>
       </c>
       <c r="AA266" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB266" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AC266" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC266" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD266" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE266" t="s" s="2">
-        <v>363</v>
+        <v>79</v>
       </c>
       <c r="AF266" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="AG266" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH266" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI266" t="s" s="2">
-        <v>417</v>
+        <v>79</v>
       </c>
       <c r="AJ266" t="s" s="2">
         <v>103</v>
@@ -34187,10 +34201,10 @@
         <v>79</v>
       </c>
       <c r="AL266" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="AM266" t="s" s="2">
-        <v>419</v>
+        <v>168</v>
       </c>
       <c r="AN266" t="s" s="2">
         <v>79</v>
@@ -34201,14 +34215,12 @@
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B267" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="C267" t="s" s="2">
-        <v>723</v>
-      </c>
+      <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
         <v>79</v>
       </c>
@@ -34276,16 +34288,14 @@
         <v>79</v>
       </c>
       <c r="AB267" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC267" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="AC267" s="2"/>
       <c r="AD267" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE267" t="s" s="2">
-        <v>79</v>
+        <v>363</v>
       </c>
       <c r="AF267" t="s" s="2">
         <v>413</v>
@@ -34445,7 +34455,7 @@
         <v>413</v>
       </c>
       <c r="C269" t="s" s="2">
-        <v>462</v>
+        <v>729</v>
       </c>
       <c r="D269" t="s" s="2">
         <v>79</v>
@@ -34467,7 +34477,7 @@
         <v>79</v>
       </c>
       <c r="K269" t="s" s="2">
-        <v>463</v>
+        <v>730</v>
       </c>
       <c r="L269" t="s" s="2">
         <v>414</v>
@@ -34558,12 +34568,14 @@
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="C270" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="C270" t="s" s="2">
+        <v>462</v>
+      </c>
       <c r="D270" t="s" s="2">
         <v>79</v>
       </c>
@@ -34572,7 +34584,7 @@
         <v>80</v>
       </c>
       <c r="G270" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H270" t="s" s="2">
         <v>79</v>
@@ -34584,20 +34596,18 @@
         <v>79</v>
       </c>
       <c r="K270" t="s" s="2">
-        <v>172</v>
+        <v>463</v>
       </c>
       <c r="L270" t="s" s="2">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="M270" t="s" s="2">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="N270" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O270" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="O270" s="2"/>
       <c r="P270" t="s" s="2">
         <v>79</v>
       </c>
@@ -34621,13 +34631,13 @@
         <v>79</v>
       </c>
       <c r="X270" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="Y270" t="s" s="2">
-        <v>425</v>
+        <v>79</v>
       </c>
       <c r="Z270" t="s" s="2">
-        <v>426</v>
+        <v>79</v>
       </c>
       <c r="AA270" t="s" s="2">
         <v>79</v>
@@ -34645,13 +34655,13 @@
         <v>79</v>
       </c>
       <c r="AF270" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="AG270" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH270" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI270" t="s" s="2">
         <v>417</v>
@@ -34663,10 +34673,10 @@
         <v>79</v>
       </c>
       <c r="AL270" t="s" s="2">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="AM270" t="s" s="2">
-        <v>168</v>
+        <v>419</v>
       </c>
       <c r="AN270" t="s" s="2">
         <v>79</v>
@@ -34677,10 +34687,10 @@
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -34691,7 +34701,7 @@
         <v>80</v>
       </c>
       <c r="G271" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H271" t="s" s="2">
         <v>79</v>
@@ -34703,18 +34713,20 @@
         <v>79</v>
       </c>
       <c r="K271" t="s" s="2">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="L271" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="M271" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="N271" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O271" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="O271" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P271" t="s" s="2">
         <v>79</v>
       </c>
@@ -34738,13 +34750,13 @@
         <v>79</v>
       </c>
       <c r="X271" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="Y271" t="s" s="2">
-        <v>79</v>
+        <v>425</v>
       </c>
       <c r="Z271" t="s" s="2">
-        <v>79</v>
+        <v>426</v>
       </c>
       <c r="AA271" t="s" s="2">
         <v>79</v>
@@ -34762,16 +34774,16 @@
         <v>79</v>
       </c>
       <c r="AF271" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="AG271" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH271" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI271" t="s" s="2">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="AJ271" t="s" s="2">
         <v>103</v>
@@ -34780,10 +34792,10 @@
         <v>79</v>
       </c>
       <c r="AL271" t="s" s="2">
-        <v>365</v>
+        <v>427</v>
       </c>
       <c r="AM271" t="s" s="2">
-        <v>432</v>
+        <v>168</v>
       </c>
       <c r="AN271" t="s" s="2">
         <v>79</v>
@@ -34794,14 +34806,12 @@
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="C272" t="s" s="2">
-        <v>732</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
         <v>79</v>
       </c>
@@ -34810,7 +34820,7 @@
         <v>80</v>
       </c>
       <c r="G272" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H272" t="s" s="2">
         <v>79</v>
@@ -34822,15 +34832,17 @@
         <v>79</v>
       </c>
       <c r="K272" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="L272" t="s" s="2">
-        <v>360</v>
+        <v>429</v>
       </c>
       <c r="M272" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N272" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="N272" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="O272" s="2"/>
       <c r="P272" t="s" s="2">
         <v>79</v>
@@ -34879,7 +34891,7 @@
         <v>79</v>
       </c>
       <c r="AF272" t="s" s="2">
-        <v>358</v>
+        <v>428</v>
       </c>
       <c r="AG272" t="s" s="2">
         <v>80</v>
@@ -34888,10 +34900,10 @@
         <v>81</v>
       </c>
       <c r="AI272" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="AJ272" t="s" s="2">
-        <v>364</v>
+        <v>103</v>
       </c>
       <c r="AK272" t="s" s="2">
         <v>79</v>
@@ -34900,7 +34912,7 @@
         <v>365</v>
       </c>
       <c r="AM272" t="s" s="2">
-        <v>366</v>
+        <v>432</v>
       </c>
       <c r="AN272" t="s" s="2">
         <v>79</v>
@@ -34911,12 +34923,14 @@
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C273" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="C273" t="s" s="2">
+        <v>735</v>
+      </c>
       <c r="D273" t="s" s="2">
         <v>79</v>
       </c>
@@ -34937,13 +34951,13 @@
         <v>79</v>
       </c>
       <c r="K273" t="s" s="2">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="L273" t="s" s="2">
-        <v>262</v>
+        <v>360</v>
       </c>
       <c r="M273" t="s" s="2">
-        <v>263</v>
+        <v>361</v>
       </c>
       <c r="N273" s="2"/>
       <c r="O273" s="2"/>
@@ -34994,28 +35008,28 @@
         <v>79</v>
       </c>
       <c r="AF273" t="s" s="2">
-        <v>264</v>
+        <v>358</v>
       </c>
       <c r="AG273" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH273" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI273" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ273" t="s" s="2">
-        <v>79</v>
+        <v>364</v>
       </c>
       <c r="AK273" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL273" t="s" s="2">
-        <v>168</v>
+        <v>365</v>
       </c>
       <c r="AM273" t="s" s="2">
-        <v>79</v>
+        <v>366</v>
       </c>
       <c r="AN273" t="s" s="2">
         <v>79</v>
@@ -35026,21 +35040,21 @@
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E274" s="2"/>
       <c r="F274" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G274" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H274" t="s" s="2">
         <v>79</v>
@@ -35052,17 +35066,15 @@
         <v>79</v>
       </c>
       <c r="K274" t="s" s="2">
-        <v>137</v>
+        <v>237</v>
       </c>
       <c r="L274" t="s" s="2">
-        <v>138</v>
+        <v>262</v>
       </c>
       <c r="M274" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N274" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N274" s="2"/>
       <c r="O274" s="2"/>
       <c r="P274" t="s" s="2">
         <v>79</v>
@@ -35111,19 +35123,19 @@
         <v>79</v>
       </c>
       <c r="AF274" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AG274" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH274" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI274" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ274" t="s" s="2">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="AK274" t="s" s="2">
         <v>79</v>
@@ -35143,14 +35155,14 @@
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
-        <v>269</v>
+        <v>136</v>
       </c>
       <c r="E275" s="2"/>
       <c r="F275" t="s" s="2">
@@ -35163,26 +35175,24 @@
         <v>79</v>
       </c>
       <c r="I275" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J275" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K275" t="s" s="2">
         <v>137</v>
       </c>
       <c r="L275" t="s" s="2">
-        <v>270</v>
+        <v>138</v>
       </c>
       <c r="M275" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="N275" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="O275" t="s" s="2">
-        <v>146</v>
-      </c>
+      <c r="O275" s="2"/>
       <c r="P275" t="s" s="2">
         <v>79</v>
       </c>
@@ -35230,7 +35240,7 @@
         <v>79</v>
       </c>
       <c r="AF275" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="AG275" t="s" s="2">
         <v>80</v>
@@ -35248,7 +35258,7 @@
         <v>79</v>
       </c>
       <c r="AL275" t="s" s="2">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="AM275" t="s" s="2">
         <v>79</v>
@@ -35262,45 +35272,45 @@
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
-        <v>371</v>
+        <v>269</v>
       </c>
       <c r="E276" s="2"/>
       <c r="F276" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G276" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H276" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I276" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J276" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K276" t="s" s="2">
-        <v>237</v>
+        <v>137</v>
       </c>
       <c r="L276" t="s" s="2">
-        <v>372</v>
+        <v>270</v>
       </c>
       <c r="M276" t="s" s="2">
-        <v>373</v>
+        <v>271</v>
       </c>
       <c r="N276" t="s" s="2">
-        <v>374</v>
+        <v>140</v>
       </c>
       <c r="O276" t="s" s="2">
-        <v>375</v>
+        <v>146</v>
       </c>
       <c r="P276" t="s" s="2">
         <v>79</v>
@@ -35349,28 +35359,28 @@
         <v>79</v>
       </c>
       <c r="AF276" t="s" s="2">
-        <v>370</v>
+        <v>272</v>
       </c>
       <c r="AG276" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH276" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI276" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ276" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK276" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL276" t="s" s="2">
-        <v>241</v>
+        <v>134</v>
       </c>
       <c r="AM276" t="s" s="2">
-        <v>242</v>
+        <v>79</v>
       </c>
       <c r="AN276" t="s" s="2">
         <v>79</v>
@@ -35381,18 +35391,18 @@
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
-        <v>79</v>
+        <v>371</v>
       </c>
       <c r="E277" s="2"/>
       <c r="F277" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G277" t="s" s="2">
         <v>91</v>
@@ -35407,19 +35417,19 @@
         <v>79</v>
       </c>
       <c r="K277" t="s" s="2">
-        <v>172</v>
+        <v>237</v>
       </c>
       <c r="L277" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="M277" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="N277" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="O277" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="P277" t="s" s="2">
         <v>79</v>
@@ -35429,7 +35439,7 @@
         <v>79</v>
       </c>
       <c r="S277" t="s" s="2">
-        <v>738</v>
+        <v>79</v>
       </c>
       <c r="T277" t="s" s="2">
         <v>79</v>
@@ -35444,13 +35454,13 @@
         <v>79</v>
       </c>
       <c r="X277" t="s" s="2">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="Y277" t="s" s="2">
-        <v>381</v>
+        <v>79</v>
       </c>
       <c r="Z277" t="s" s="2">
-        <v>382</v>
+        <v>79</v>
       </c>
       <c r="AA277" t="s" s="2">
         <v>79</v>
@@ -35468,7 +35478,7 @@
         <v>79</v>
       </c>
       <c r="AF277" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="AG277" t="s" s="2">
         <v>80</v>
@@ -35486,10 +35496,10 @@
         <v>79</v>
       </c>
       <c r="AL277" t="s" s="2">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="AM277" t="s" s="2">
-        <v>181</v>
+        <v>242</v>
       </c>
       <c r="AN277" t="s" s="2">
         <v>79</v>
@@ -35500,10 +35510,10 @@
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -35511,10 +35521,10 @@
       </c>
       <c r="E278" s="2"/>
       <c r="F278" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G278" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H278" t="s" s="2">
         <v>79</v>
@@ -35526,17 +35536,19 @@
         <v>79</v>
       </c>
       <c r="K278" t="s" s="2">
-        <v>227</v>
+        <v>172</v>
       </c>
       <c r="L278" t="s" s="2">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="M278" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N278" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N278" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="O278" t="s" s="2">
-        <v>230</v>
+        <v>380</v>
       </c>
       <c r="P278" t="s" s="2">
         <v>79</v>
@@ -35546,7 +35558,7 @@
         <v>79</v>
       </c>
       <c r="S278" t="s" s="2">
-        <v>79</v>
+        <v>741</v>
       </c>
       <c r="T278" t="s" s="2">
         <v>79</v>
@@ -35561,13 +35573,13 @@
         <v>79</v>
       </c>
       <c r="X278" t="s" s="2">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="Y278" t="s" s="2">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="Z278" t="s" s="2">
-        <v>79</v>
+        <v>382</v>
       </c>
       <c r="AA278" t="s" s="2">
         <v>79</v>
@@ -35585,13 +35597,13 @@
         <v>79</v>
       </c>
       <c r="AF278" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="AG278" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH278" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI278" t="s" s="2">
         <v>79</v>
@@ -35603,24 +35615,24 @@
         <v>79</v>
       </c>
       <c r="AL278" t="s" s="2">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="AM278" t="s" s="2">
-        <v>233</v>
+        <v>181</v>
       </c>
       <c r="AN278" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO278" t="s" s="2">
-        <v>235</v>
+        <v>79</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -35631,7 +35643,7 @@
         <v>80</v>
       </c>
       <c r="G279" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H279" t="s" s="2">
         <v>79</v>
@@ -35643,18 +35655,18 @@
         <v>79</v>
       </c>
       <c r="K279" t="s" s="2">
-        <v>354</v>
+        <v>227</v>
       </c>
       <c r="L279" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="M279" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N279" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O279" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N279" s="2"/>
+      <c r="O279" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P279" t="s" s="2">
         <v>79</v>
       </c>
@@ -35702,13 +35714,13 @@
         <v>79</v>
       </c>
       <c r="AF279" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AG279" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH279" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI279" t="s" s="2">
         <v>79</v>
@@ -35720,24 +35732,24 @@
         <v>79</v>
       </c>
       <c r="AL279" t="s" s="2">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="AM279" t="s" s="2">
-        <v>390</v>
+        <v>233</v>
       </c>
       <c r="AN279" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO279" t="s" s="2">
-        <v>79</v>
+        <v>235</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -35760,16 +35772,16 @@
         <v>79</v>
       </c>
       <c r="K280" t="s" s="2">
-        <v>121</v>
+        <v>354</v>
       </c>
       <c r="L280" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="M280" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="N280" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="O280" s="2"/>
       <c r="P280" t="s" s="2">
@@ -35819,7 +35831,7 @@
         <v>79</v>
       </c>
       <c r="AF280" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AG280" t="s" s="2">
         <v>80</v>
@@ -35828,7 +35840,7 @@
         <v>91</v>
       </c>
       <c r="AI280" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="AJ280" t="s" s="2">
         <v>103</v>
@@ -35837,10 +35849,10 @@
         <v>79</v>
       </c>
       <c r="AL280" t="s" s="2">
-        <v>396</v>
+        <v>79</v>
       </c>
       <c r="AM280" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="AN280" t="s" s="2">
         <v>79</v>
@@ -35851,10 +35863,10 @@
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
@@ -35877,20 +35889,18 @@
         <v>79</v>
       </c>
       <c r="K281" t="s" s="2">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="L281" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="M281" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="N281" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O281" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="O281" s="2"/>
       <c r="P281" t="s" s="2">
         <v>79</v>
       </c>
@@ -35914,13 +35924,13 @@
         <v>79</v>
       </c>
       <c r="X281" t="s" s="2">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="Y281" t="s" s="2">
-        <v>402</v>
+        <v>79</v>
       </c>
       <c r="Z281" t="s" s="2">
-        <v>403</v>
+        <v>79</v>
       </c>
       <c r="AA281" t="s" s="2">
         <v>79</v>
@@ -35938,7 +35948,7 @@
         <v>79</v>
       </c>
       <c r="AF281" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="AG281" t="s" s="2">
         <v>80</v>
@@ -35947,7 +35957,7 @@
         <v>91</v>
       </c>
       <c r="AI281" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="AJ281" t="s" s="2">
         <v>103</v>
@@ -35956,24 +35966,24 @@
         <v>79</v>
       </c>
       <c r="AL281" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="AM281" t="s" s="2">
-        <v>168</v>
+        <v>396</v>
       </c>
       <c r="AN281" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO281" t="s" s="2">
-        <v>183</v>
+        <v>79</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" t="s" s="2">
@@ -35996,19 +36006,19 @@
         <v>79</v>
       </c>
       <c r="K282" t="s" s="2">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="M282" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="N282" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="O282" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="P282" t="s" s="2">
         <v>79</v>
@@ -36033,13 +36043,13 @@
         <v>79</v>
       </c>
       <c r="X282" t="s" s="2">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="Y282" t="s" s="2">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="Z282" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="AA282" t="s" s="2">
         <v>79</v>
@@ -36057,7 +36067,7 @@
         <v>79</v>
       </c>
       <c r="AF282" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="AG282" t="s" s="2">
         <v>80</v>
@@ -36075,7 +36085,7 @@
         <v>79</v>
       </c>
       <c r="AL282" t="s" s="2">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="AM282" t="s" s="2">
         <v>168</v>
@@ -36084,15 +36094,15 @@
         <v>79</v>
       </c>
       <c r="AO282" t="s" s="2">
-        <v>79</v>
+        <v>183</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -36103,7 +36113,7 @@
         <v>80</v>
       </c>
       <c r="G283" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H283" t="s" s="2">
         <v>79</v>
@@ -36115,18 +36125,20 @@
         <v>79</v>
       </c>
       <c r="K283" t="s" s="2">
-        <v>745</v>
+        <v>172</v>
       </c>
       <c r="L283" t="s" s="2">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="M283" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="N283" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O283" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="O283" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P283" t="s" s="2">
         <v>79</v>
       </c>
@@ -36150,38 +36162,40 @@
         <v>79</v>
       </c>
       <c r="X283" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="Y283" t="s" s="2">
-        <v>79</v>
+        <v>410</v>
       </c>
       <c r="Z283" t="s" s="2">
-        <v>79</v>
+        <v>411</v>
       </c>
       <c r="AA283" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB283" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AC283" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC283" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD283" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE283" t="s" s="2">
-        <v>363</v>
+        <v>79</v>
       </c>
       <c r="AF283" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="AG283" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH283" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI283" t="s" s="2">
-        <v>417</v>
+        <v>79</v>
       </c>
       <c r="AJ283" t="s" s="2">
         <v>103</v>
@@ -36190,10 +36204,10 @@
         <v>79</v>
       </c>
       <c r="AL283" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="AM283" t="s" s="2">
-        <v>419</v>
+        <v>168</v>
       </c>
       <c r="AN283" t="s" s="2">
         <v>79</v>
@@ -36204,14 +36218,12 @@
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B284" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="C284" t="s" s="2">
-        <v>747</v>
-      </c>
+      <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
         <v>79</v>
       </c>
@@ -36279,16 +36291,14 @@
         <v>79</v>
       </c>
       <c r="AB284" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC284" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="AC284" s="2"/>
       <c r="AD284" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE284" t="s" s="2">
-        <v>79</v>
+        <v>363</v>
       </c>
       <c r="AF284" t="s" s="2">
         <v>413</v>
@@ -36329,7 +36339,7 @@
         <v>413</v>
       </c>
       <c r="C285" t="s" s="2">
-        <v>462</v>
+        <v>750</v>
       </c>
       <c r="D285" t="s" s="2">
         <v>79</v>
@@ -36351,7 +36361,7 @@
         <v>79</v>
       </c>
       <c r="K285" t="s" s="2">
-        <v>463</v>
+        <v>751</v>
       </c>
       <c r="L285" t="s" s="2">
         <v>414</v>
@@ -36442,12 +36452,14 @@
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="C286" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="C286" t="s" s="2">
+        <v>462</v>
+      </c>
       <c r="D286" t="s" s="2">
         <v>79</v>
       </c>
@@ -36456,7 +36468,7 @@
         <v>80</v>
       </c>
       <c r="G286" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H286" t="s" s="2">
         <v>79</v>
@@ -36468,20 +36480,18 @@
         <v>79</v>
       </c>
       <c r="K286" t="s" s="2">
-        <v>172</v>
+        <v>463</v>
       </c>
       <c r="L286" t="s" s="2">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="M286" t="s" s="2">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="N286" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O286" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="O286" s="2"/>
       <c r="P286" t="s" s="2">
         <v>79</v>
       </c>
@@ -36505,13 +36515,13 @@
         <v>79</v>
       </c>
       <c r="X286" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="Y286" t="s" s="2">
-        <v>425</v>
+        <v>79</v>
       </c>
       <c r="Z286" t="s" s="2">
-        <v>426</v>
+        <v>79</v>
       </c>
       <c r="AA286" t="s" s="2">
         <v>79</v>
@@ -36529,13 +36539,13 @@
         <v>79</v>
       </c>
       <c r="AF286" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="AG286" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH286" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI286" t="s" s="2">
         <v>417</v>
@@ -36547,10 +36557,10 @@
         <v>79</v>
       </c>
       <c r="AL286" t="s" s="2">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="AM286" t="s" s="2">
-        <v>168</v>
+        <v>419</v>
       </c>
       <c r="AN286" t="s" s="2">
         <v>79</v>
@@ -36561,10 +36571,10 @@
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
@@ -36575,7 +36585,7 @@
         <v>80</v>
       </c>
       <c r="G287" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H287" t="s" s="2">
         <v>79</v>
@@ -36587,18 +36597,20 @@
         <v>79</v>
       </c>
       <c r="K287" t="s" s="2">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="L287" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="M287" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="N287" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O287" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="O287" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P287" t="s" s="2">
         <v>79</v>
       </c>
@@ -36622,13 +36634,13 @@
         <v>79</v>
       </c>
       <c r="X287" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="Y287" t="s" s="2">
-        <v>79</v>
+        <v>425</v>
       </c>
       <c r="Z287" t="s" s="2">
-        <v>79</v>
+        <v>426</v>
       </c>
       <c r="AA287" t="s" s="2">
         <v>79</v>
@@ -36646,16 +36658,16 @@
         <v>79</v>
       </c>
       <c r="AF287" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="AG287" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH287" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI287" t="s" s="2">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="AJ287" t="s" s="2">
         <v>103</v>
@@ -36664,10 +36676,10 @@
         <v>79</v>
       </c>
       <c r="AL287" t="s" s="2">
-        <v>365</v>
+        <v>427</v>
       </c>
       <c r="AM287" t="s" s="2">
-        <v>432</v>
+        <v>168</v>
       </c>
       <c r="AN287" t="s" s="2">
         <v>79</v>
@@ -36678,14 +36690,12 @@
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="C288" t="s" s="2">
-        <v>753</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
         <v>79</v>
       </c>
@@ -36694,7 +36704,7 @@
         <v>80</v>
       </c>
       <c r="G288" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H288" t="s" s="2">
         <v>79</v>
@@ -36706,15 +36716,17 @@
         <v>79</v>
       </c>
       <c r="K288" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="L288" t="s" s="2">
-        <v>360</v>
+        <v>429</v>
       </c>
       <c r="M288" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N288" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="N288" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="O288" s="2"/>
       <c r="P288" t="s" s="2">
         <v>79</v>
@@ -36763,7 +36775,7 @@
         <v>79</v>
       </c>
       <c r="AF288" t="s" s="2">
-        <v>358</v>
+        <v>428</v>
       </c>
       <c r="AG288" t="s" s="2">
         <v>80</v>
@@ -36772,10 +36784,10 @@
         <v>81</v>
       </c>
       <c r="AI288" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="AJ288" t="s" s="2">
-        <v>364</v>
+        <v>103</v>
       </c>
       <c r="AK288" t="s" s="2">
         <v>79</v>
@@ -36784,7 +36796,7 @@
         <v>365</v>
       </c>
       <c r="AM288" t="s" s="2">
-        <v>366</v>
+        <v>432</v>
       </c>
       <c r="AN288" t="s" s="2">
         <v>79</v>
@@ -36795,12 +36807,14 @@
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C289" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="C289" t="s" s="2">
+        <v>756</v>
+      </c>
       <c r="D289" t="s" s="2">
         <v>79</v>
       </c>
@@ -36821,13 +36835,13 @@
         <v>79</v>
       </c>
       <c r="K289" t="s" s="2">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="L289" t="s" s="2">
-        <v>262</v>
+        <v>360</v>
       </c>
       <c r="M289" t="s" s="2">
-        <v>263</v>
+        <v>361</v>
       </c>
       <c r="N289" s="2"/>
       <c r="O289" s="2"/>
@@ -36878,28 +36892,28 @@
         <v>79</v>
       </c>
       <c r="AF289" t="s" s="2">
-        <v>264</v>
+        <v>358</v>
       </c>
       <c r="AG289" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH289" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI289" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ289" t="s" s="2">
-        <v>79</v>
+        <v>364</v>
       </c>
       <c r="AK289" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL289" t="s" s="2">
-        <v>168</v>
+        <v>365</v>
       </c>
       <c r="AM289" t="s" s="2">
-        <v>79</v>
+        <v>366</v>
       </c>
       <c r="AN289" t="s" s="2">
         <v>79</v>
@@ -36910,21 +36924,21 @@
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E290" s="2"/>
       <c r="F290" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G290" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H290" t="s" s="2">
         <v>79</v>
@@ -36936,17 +36950,15 @@
         <v>79</v>
       </c>
       <c r="K290" t="s" s="2">
-        <v>137</v>
+        <v>237</v>
       </c>
       <c r="L290" t="s" s="2">
-        <v>138</v>
+        <v>262</v>
       </c>
       <c r="M290" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N290" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N290" s="2"/>
       <c r="O290" s="2"/>
       <c r="P290" t="s" s="2">
         <v>79</v>
@@ -36995,19 +37007,19 @@
         <v>79</v>
       </c>
       <c r="AF290" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AG290" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH290" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI290" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ290" t="s" s="2">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="AK290" t="s" s="2">
         <v>79</v>
@@ -37027,14 +37039,14 @@
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C291" s="2"/>
       <c r="D291" t="s" s="2">
-        <v>269</v>
+        <v>136</v>
       </c>
       <c r="E291" s="2"/>
       <c r="F291" t="s" s="2">
@@ -37047,26 +37059,24 @@
         <v>79</v>
       </c>
       <c r="I291" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J291" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K291" t="s" s="2">
         <v>137</v>
       </c>
       <c r="L291" t="s" s="2">
-        <v>270</v>
+        <v>138</v>
       </c>
       <c r="M291" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="N291" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="O291" t="s" s="2">
-        <v>146</v>
-      </c>
+      <c r="O291" s="2"/>
       <c r="P291" t="s" s="2">
         <v>79</v>
       </c>
@@ -37114,7 +37124,7 @@
         <v>79</v>
       </c>
       <c r="AF291" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="AG291" t="s" s="2">
         <v>80</v>
@@ -37132,7 +37142,7 @@
         <v>79</v>
       </c>
       <c r="AL291" t="s" s="2">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="AM291" t="s" s="2">
         <v>79</v>
@@ -37146,45 +37156,45 @@
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C292" s="2"/>
       <c r="D292" t="s" s="2">
-        <v>371</v>
+        <v>269</v>
       </c>
       <c r="E292" s="2"/>
       <c r="F292" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G292" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H292" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I292" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J292" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K292" t="s" s="2">
-        <v>237</v>
+        <v>137</v>
       </c>
       <c r="L292" t="s" s="2">
-        <v>372</v>
+        <v>270</v>
       </c>
       <c r="M292" t="s" s="2">
-        <v>373</v>
+        <v>271</v>
       </c>
       <c r="N292" t="s" s="2">
-        <v>374</v>
+        <v>140</v>
       </c>
       <c r="O292" t="s" s="2">
-        <v>375</v>
+        <v>146</v>
       </c>
       <c r="P292" t="s" s="2">
         <v>79</v>
@@ -37233,28 +37243,28 @@
         <v>79</v>
       </c>
       <c r="AF292" t="s" s="2">
-        <v>370</v>
+        <v>272</v>
       </c>
       <c r="AG292" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH292" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI292" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ292" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK292" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL292" t="s" s="2">
-        <v>241</v>
+        <v>134</v>
       </c>
       <c r="AM292" t="s" s="2">
-        <v>242</v>
+        <v>79</v>
       </c>
       <c r="AN292" t="s" s="2">
         <v>79</v>
@@ -37265,18 +37275,18 @@
     </row>
     <row r="293">
       <c r="A293" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C293" s="2"/>
       <c r="D293" t="s" s="2">
-        <v>79</v>
+        <v>371</v>
       </c>
       <c r="E293" s="2"/>
       <c r="F293" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G293" t="s" s="2">
         <v>91</v>
@@ -37291,19 +37301,19 @@
         <v>79</v>
       </c>
       <c r="K293" t="s" s="2">
-        <v>172</v>
+        <v>237</v>
       </c>
       <c r="L293" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="M293" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="N293" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="O293" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="P293" t="s" s="2">
         <v>79</v>
@@ -37313,7 +37323,7 @@
         <v>79</v>
       </c>
       <c r="S293" t="s" s="2">
-        <v>759</v>
+        <v>79</v>
       </c>
       <c r="T293" t="s" s="2">
         <v>79</v>
@@ -37328,13 +37338,13 @@
         <v>79</v>
       </c>
       <c r="X293" t="s" s="2">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="Y293" t="s" s="2">
-        <v>381</v>
+        <v>79</v>
       </c>
       <c r="Z293" t="s" s="2">
-        <v>382</v>
+        <v>79</v>
       </c>
       <c r="AA293" t="s" s="2">
         <v>79</v>
@@ -37352,7 +37362,7 @@
         <v>79</v>
       </c>
       <c r="AF293" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="AG293" t="s" s="2">
         <v>80</v>
@@ -37370,10 +37380,10 @@
         <v>79</v>
       </c>
       <c r="AL293" t="s" s="2">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="AM293" t="s" s="2">
-        <v>181</v>
+        <v>242</v>
       </c>
       <c r="AN293" t="s" s="2">
         <v>79</v>
@@ -37384,10 +37394,10 @@
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="C294" s="2"/>
       <c r="D294" t="s" s="2">
@@ -37395,10 +37405,10 @@
       </c>
       <c r="E294" s="2"/>
       <c r="F294" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G294" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H294" t="s" s="2">
         <v>79</v>
@@ -37410,17 +37420,19 @@
         <v>79</v>
       </c>
       <c r="K294" t="s" s="2">
-        <v>227</v>
+        <v>172</v>
       </c>
       <c r="L294" t="s" s="2">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="M294" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N294" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N294" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="O294" t="s" s="2">
-        <v>230</v>
+        <v>380</v>
       </c>
       <c r="P294" t="s" s="2">
         <v>79</v>
@@ -37430,7 +37442,7 @@
         <v>79</v>
       </c>
       <c r="S294" t="s" s="2">
-        <v>79</v>
+        <v>762</v>
       </c>
       <c r="T294" t="s" s="2">
         <v>79</v>
@@ -37445,13 +37457,13 @@
         <v>79</v>
       </c>
       <c r="X294" t="s" s="2">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="Y294" t="s" s="2">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="Z294" t="s" s="2">
-        <v>79</v>
+        <v>382</v>
       </c>
       <c r="AA294" t="s" s="2">
         <v>79</v>
@@ -37469,13 +37481,13 @@
         <v>79</v>
       </c>
       <c r="AF294" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="AG294" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH294" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI294" t="s" s="2">
         <v>79</v>
@@ -37487,24 +37499,24 @@
         <v>79</v>
       </c>
       <c r="AL294" t="s" s="2">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="AM294" t="s" s="2">
-        <v>233</v>
+        <v>181</v>
       </c>
       <c r="AN294" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO294" t="s" s="2">
-        <v>235</v>
+        <v>79</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" t="s" s="2">
@@ -37515,7 +37527,7 @@
         <v>80</v>
       </c>
       <c r="G295" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H295" t="s" s="2">
         <v>79</v>
@@ -37527,18 +37539,18 @@
         <v>79</v>
       </c>
       <c r="K295" t="s" s="2">
-        <v>354</v>
+        <v>227</v>
       </c>
       <c r="L295" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="M295" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N295" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O295" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N295" s="2"/>
+      <c r="O295" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P295" t="s" s="2">
         <v>79</v>
       </c>
@@ -37586,13 +37598,13 @@
         <v>79</v>
       </c>
       <c r="AF295" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AG295" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH295" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI295" t="s" s="2">
         <v>79</v>
@@ -37604,24 +37616,24 @@
         <v>79</v>
       </c>
       <c r="AL295" t="s" s="2">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="AM295" t="s" s="2">
-        <v>390</v>
+        <v>233</v>
       </c>
       <c r="AN295" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO295" t="s" s="2">
-        <v>79</v>
+        <v>235</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" t="s" s="2">
@@ -37644,16 +37656,16 @@
         <v>79</v>
       </c>
       <c r="K296" t="s" s="2">
-        <v>121</v>
+        <v>354</v>
       </c>
       <c r="L296" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="M296" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="N296" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="O296" s="2"/>
       <c r="P296" t="s" s="2">
@@ -37703,7 +37715,7 @@
         <v>79</v>
       </c>
       <c r="AF296" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AG296" t="s" s="2">
         <v>80</v>
@@ -37712,7 +37724,7 @@
         <v>91</v>
       </c>
       <c r="AI296" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="AJ296" t="s" s="2">
         <v>103</v>
@@ -37721,10 +37733,10 @@
         <v>79</v>
       </c>
       <c r="AL296" t="s" s="2">
-        <v>396</v>
+        <v>79</v>
       </c>
       <c r="AM296" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="AN296" t="s" s="2">
         <v>79</v>
@@ -37735,10 +37747,10 @@
     </row>
     <row r="297">
       <c r="A297" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C297" s="2"/>
       <c r="D297" t="s" s="2">
@@ -37761,20 +37773,18 @@
         <v>79</v>
       </c>
       <c r="K297" t="s" s="2">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="L297" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="M297" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="N297" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O297" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="O297" s="2"/>
       <c r="P297" t="s" s="2">
         <v>79</v>
       </c>
@@ -37798,13 +37808,13 @@
         <v>79</v>
       </c>
       <c r="X297" t="s" s="2">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="Y297" t="s" s="2">
-        <v>402</v>
+        <v>79</v>
       </c>
       <c r="Z297" t="s" s="2">
-        <v>403</v>
+        <v>79</v>
       </c>
       <c r="AA297" t="s" s="2">
         <v>79</v>
@@ -37822,7 +37832,7 @@
         <v>79</v>
       </c>
       <c r="AF297" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="AG297" t="s" s="2">
         <v>80</v>
@@ -37831,7 +37841,7 @@
         <v>91</v>
       </c>
       <c r="AI297" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="AJ297" t="s" s="2">
         <v>103</v>
@@ -37840,24 +37850,24 @@
         <v>79</v>
       </c>
       <c r="AL297" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="AM297" t="s" s="2">
-        <v>168</v>
+        <v>396</v>
       </c>
       <c r="AN297" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO297" t="s" s="2">
-        <v>183</v>
+        <v>79</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C298" s="2"/>
       <c r="D298" t="s" s="2">
@@ -37880,19 +37890,19 @@
         <v>79</v>
       </c>
       <c r="K298" t="s" s="2">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="L298" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="M298" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="N298" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="O298" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="P298" t="s" s="2">
         <v>79</v>
@@ -37917,13 +37927,13 @@
         <v>79</v>
       </c>
       <c r="X298" t="s" s="2">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="Y298" t="s" s="2">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="Z298" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="AA298" t="s" s="2">
         <v>79</v>
@@ -37941,7 +37951,7 @@
         <v>79</v>
       </c>
       <c r="AF298" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="AG298" t="s" s="2">
         <v>80</v>
@@ -37959,7 +37969,7 @@
         <v>79</v>
       </c>
       <c r="AL298" t="s" s="2">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="AM298" t="s" s="2">
         <v>168</v>
@@ -37968,15 +37978,15 @@
         <v>79</v>
       </c>
       <c r="AO298" t="s" s="2">
-        <v>79</v>
+        <v>183</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="C299" s="2"/>
       <c r="D299" t="s" s="2">
@@ -37987,7 +37997,7 @@
         <v>80</v>
       </c>
       <c r="G299" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H299" t="s" s="2">
         <v>79</v>
@@ -37999,18 +38009,20 @@
         <v>79</v>
       </c>
       <c r="K299" t="s" s="2">
-        <v>766</v>
+        <v>172</v>
       </c>
       <c r="L299" t="s" s="2">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="M299" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="N299" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O299" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="O299" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P299" t="s" s="2">
         <v>79</v>
       </c>
@@ -38034,38 +38046,40 @@
         <v>79</v>
       </c>
       <c r="X299" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="Y299" t="s" s="2">
-        <v>79</v>
+        <v>410</v>
       </c>
       <c r="Z299" t="s" s="2">
-        <v>79</v>
+        <v>411</v>
       </c>
       <c r="AA299" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB299" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AC299" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC299" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD299" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE299" t="s" s="2">
-        <v>363</v>
+        <v>79</v>
       </c>
       <c r="AF299" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="AG299" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH299" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI299" t="s" s="2">
-        <v>417</v>
+        <v>79</v>
       </c>
       <c r="AJ299" t="s" s="2">
         <v>103</v>
@@ -38074,10 +38088,10 @@
         <v>79</v>
       </c>
       <c r="AL299" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="AM299" t="s" s="2">
-        <v>419</v>
+        <v>168</v>
       </c>
       <c r="AN299" t="s" s="2">
         <v>79</v>
@@ -38088,14 +38102,12 @@
     </row>
     <row r="300">
       <c r="A300" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B300" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="C300" t="s" s="2">
-        <v>768</v>
-      </c>
+      <c r="C300" s="2"/>
       <c r="D300" t="s" s="2">
         <v>79</v>
       </c>
@@ -38163,16 +38175,14 @@
         <v>79</v>
       </c>
       <c r="AB300" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC300" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="AC300" s="2"/>
       <c r="AD300" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE300" t="s" s="2">
-        <v>79</v>
+        <v>363</v>
       </c>
       <c r="AF300" t="s" s="2">
         <v>413</v>
@@ -38213,7 +38223,7 @@
         <v>413</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>462</v>
+        <v>771</v>
       </c>
       <c r="D301" t="s" s="2">
         <v>79</v>
@@ -38235,7 +38245,7 @@
         <v>79</v>
       </c>
       <c r="K301" t="s" s="2">
-        <v>463</v>
+        <v>772</v>
       </c>
       <c r="L301" t="s" s="2">
         <v>414</v>
@@ -38326,12 +38336,14 @@
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="C302" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="C302" t="s" s="2">
+        <v>462</v>
+      </c>
       <c r="D302" t="s" s="2">
         <v>79</v>
       </c>
@@ -38340,7 +38352,7 @@
         <v>80</v>
       </c>
       <c r="G302" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H302" t="s" s="2">
         <v>79</v>
@@ -38352,20 +38364,18 @@
         <v>79</v>
       </c>
       <c r="K302" t="s" s="2">
-        <v>172</v>
+        <v>463</v>
       </c>
       <c r="L302" t="s" s="2">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="M302" t="s" s="2">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="N302" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O302" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="O302" s="2"/>
       <c r="P302" t="s" s="2">
         <v>79</v>
       </c>
@@ -38389,13 +38399,13 @@
         <v>79</v>
       </c>
       <c r="X302" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="Y302" t="s" s="2">
-        <v>425</v>
+        <v>79</v>
       </c>
       <c r="Z302" t="s" s="2">
-        <v>426</v>
+        <v>79</v>
       </c>
       <c r="AA302" t="s" s="2">
         <v>79</v>
@@ -38413,13 +38423,13 @@
         <v>79</v>
       </c>
       <c r="AF302" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="AG302" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH302" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI302" t="s" s="2">
         <v>417</v>
@@ -38431,10 +38441,10 @@
         <v>79</v>
       </c>
       <c r="AL302" t="s" s="2">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="AM302" t="s" s="2">
-        <v>168</v>
+        <v>419</v>
       </c>
       <c r="AN302" t="s" s="2">
         <v>79</v>
@@ -38445,10 +38455,10 @@
     </row>
     <row r="303">
       <c r="A303" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C303" s="2"/>
       <c r="D303" t="s" s="2">
@@ -38459,7 +38469,7 @@
         <v>80</v>
       </c>
       <c r="G303" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H303" t="s" s="2">
         <v>79</v>
@@ -38471,18 +38481,20 @@
         <v>79</v>
       </c>
       <c r="K303" t="s" s="2">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="L303" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="M303" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="N303" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O303" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="O303" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P303" t="s" s="2">
         <v>79</v>
       </c>
@@ -38506,13 +38518,13 @@
         <v>79</v>
       </c>
       <c r="X303" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="Y303" t="s" s="2">
-        <v>79</v>
+        <v>425</v>
       </c>
       <c r="Z303" t="s" s="2">
-        <v>79</v>
+        <v>426</v>
       </c>
       <c r="AA303" t="s" s="2">
         <v>79</v>
@@ -38530,16 +38542,16 @@
         <v>79</v>
       </c>
       <c r="AF303" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="AG303" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH303" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI303" t="s" s="2">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="AJ303" t="s" s="2">
         <v>103</v>
@@ -38548,10 +38560,10 @@
         <v>79</v>
       </c>
       <c r="AL303" t="s" s="2">
-        <v>365</v>
+        <v>427</v>
       </c>
       <c r="AM303" t="s" s="2">
-        <v>432</v>
+        <v>168</v>
       </c>
       <c r="AN303" t="s" s="2">
         <v>79</v>
@@ -38562,14 +38574,12 @@
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="C304" t="s" s="2">
-        <v>774</v>
-      </c>
+        <v>428</v>
+      </c>
+      <c r="C304" s="2"/>
       <c r="D304" t="s" s="2">
         <v>79</v>
       </c>
@@ -38578,7 +38588,7 @@
         <v>80</v>
       </c>
       <c r="G304" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H304" t="s" s="2">
         <v>79</v>
@@ -38590,15 +38600,17 @@
         <v>79</v>
       </c>
       <c r="K304" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="L304" t="s" s="2">
-        <v>360</v>
+        <v>429</v>
       </c>
       <c r="M304" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N304" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="N304" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="O304" s="2"/>
       <c r="P304" t="s" s="2">
         <v>79</v>
@@ -38647,7 +38659,7 @@
         <v>79</v>
       </c>
       <c r="AF304" t="s" s="2">
-        <v>358</v>
+        <v>428</v>
       </c>
       <c r="AG304" t="s" s="2">
         <v>80</v>
@@ -38656,10 +38668,10 @@
         <v>81</v>
       </c>
       <c r="AI304" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="AJ304" t="s" s="2">
-        <v>364</v>
+        <v>103</v>
       </c>
       <c r="AK304" t="s" s="2">
         <v>79</v>
@@ -38668,7 +38680,7 @@
         <v>365</v>
       </c>
       <c r="AM304" t="s" s="2">
-        <v>366</v>
+        <v>432</v>
       </c>
       <c r="AN304" t="s" s="2">
         <v>79</v>
@@ -38679,12 +38691,14 @@
     </row>
     <row r="305">
       <c r="A305" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C305" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="C305" t="s" s="2">
+        <v>777</v>
+      </c>
       <c r="D305" t="s" s="2">
         <v>79</v>
       </c>
@@ -38705,13 +38719,13 @@
         <v>79</v>
       </c>
       <c r="K305" t="s" s="2">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="L305" t="s" s="2">
-        <v>262</v>
+        <v>360</v>
       </c>
       <c r="M305" t="s" s="2">
-        <v>263</v>
+        <v>361</v>
       </c>
       <c r="N305" s="2"/>
       <c r="O305" s="2"/>
@@ -38762,28 +38776,28 @@
         <v>79</v>
       </c>
       <c r="AF305" t="s" s="2">
-        <v>264</v>
+        <v>358</v>
       </c>
       <c r="AG305" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH305" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI305" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ305" t="s" s="2">
-        <v>79</v>
+        <v>364</v>
       </c>
       <c r="AK305" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL305" t="s" s="2">
-        <v>168</v>
+        <v>365</v>
       </c>
       <c r="AM305" t="s" s="2">
-        <v>79</v>
+        <v>366</v>
       </c>
       <c r="AN305" t="s" s="2">
         <v>79</v>
@@ -38794,21 +38808,21 @@
     </row>
     <row r="306">
       <c r="A306" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C306" s="2"/>
       <c r="D306" t="s" s="2">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E306" s="2"/>
       <c r="F306" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G306" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H306" t="s" s="2">
         <v>79</v>
@@ -38820,17 +38834,15 @@
         <v>79</v>
       </c>
       <c r="K306" t="s" s="2">
-        <v>137</v>
+        <v>237</v>
       </c>
       <c r="L306" t="s" s="2">
-        <v>138</v>
+        <v>262</v>
       </c>
       <c r="M306" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N306" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="N306" s="2"/>
       <c r="O306" s="2"/>
       <c r="P306" t="s" s="2">
         <v>79</v>
@@ -38879,19 +38891,19 @@
         <v>79</v>
       </c>
       <c r="AF306" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AG306" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH306" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI306" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ306" t="s" s="2">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="AK306" t="s" s="2">
         <v>79</v>
@@ -38911,14 +38923,14 @@
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C307" s="2"/>
       <c r="D307" t="s" s="2">
-        <v>269</v>
+        <v>136</v>
       </c>
       <c r="E307" s="2"/>
       <c r="F307" t="s" s="2">
@@ -38931,26 +38943,24 @@
         <v>79</v>
       </c>
       <c r="I307" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="J307" t="s" s="2">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K307" t="s" s="2">
         <v>137</v>
       </c>
       <c r="L307" t="s" s="2">
-        <v>270</v>
+        <v>138</v>
       </c>
       <c r="M307" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="N307" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="O307" t="s" s="2">
-        <v>146</v>
-      </c>
+      <c r="O307" s="2"/>
       <c r="P307" t="s" s="2">
         <v>79</v>
       </c>
@@ -38998,7 +39008,7 @@
         <v>79</v>
       </c>
       <c r="AF307" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="AG307" t="s" s="2">
         <v>80</v>
@@ -39016,7 +39026,7 @@
         <v>79</v>
       </c>
       <c r="AL307" t="s" s="2">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="AM307" t="s" s="2">
         <v>79</v>
@@ -39030,45 +39040,45 @@
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C308" s="2"/>
       <c r="D308" t="s" s="2">
-        <v>371</v>
+        <v>269</v>
       </c>
       <c r="E308" s="2"/>
       <c r="F308" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G308" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H308" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I308" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="J308" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K308" t="s" s="2">
-        <v>237</v>
+        <v>137</v>
       </c>
       <c r="L308" t="s" s="2">
-        <v>372</v>
+        <v>270</v>
       </c>
       <c r="M308" t="s" s="2">
-        <v>373</v>
+        <v>271</v>
       </c>
       <c r="N308" t="s" s="2">
-        <v>374</v>
+        <v>140</v>
       </c>
       <c r="O308" t="s" s="2">
-        <v>375</v>
+        <v>146</v>
       </c>
       <c r="P308" t="s" s="2">
         <v>79</v>
@@ -39117,28 +39127,28 @@
         <v>79</v>
       </c>
       <c r="AF308" t="s" s="2">
-        <v>370</v>
+        <v>272</v>
       </c>
       <c r="AG308" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH308" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI308" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ308" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK308" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL308" t="s" s="2">
-        <v>241</v>
+        <v>134</v>
       </c>
       <c r="AM308" t="s" s="2">
-        <v>242</v>
+        <v>79</v>
       </c>
       <c r="AN308" t="s" s="2">
         <v>79</v>
@@ -39149,18 +39159,18 @@
     </row>
     <row r="309">
       <c r="A309" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C309" s="2"/>
       <c r="D309" t="s" s="2">
-        <v>79</v>
+        <v>371</v>
       </c>
       <c r="E309" s="2"/>
       <c r="F309" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G309" t="s" s="2">
         <v>91</v>
@@ -39175,19 +39185,19 @@
         <v>79</v>
       </c>
       <c r="K309" t="s" s="2">
-        <v>172</v>
+        <v>237</v>
       </c>
       <c r="L309" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="M309" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="N309" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="O309" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="P309" t="s" s="2">
         <v>79</v>
@@ -39197,7 +39207,7 @@
         <v>79</v>
       </c>
       <c r="S309" t="s" s="2">
-        <v>780</v>
+        <v>79</v>
       </c>
       <c r="T309" t="s" s="2">
         <v>79</v>
@@ -39212,13 +39222,13 @@
         <v>79</v>
       </c>
       <c r="X309" t="s" s="2">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="Y309" t="s" s="2">
-        <v>381</v>
+        <v>79</v>
       </c>
       <c r="Z309" t="s" s="2">
-        <v>382</v>
+        <v>79</v>
       </c>
       <c r="AA309" t="s" s="2">
         <v>79</v>
@@ -39236,7 +39246,7 @@
         <v>79</v>
       </c>
       <c r="AF309" t="s" s="2">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="AG309" t="s" s="2">
         <v>80</v>
@@ -39254,10 +39264,10 @@
         <v>79</v>
       </c>
       <c r="AL309" t="s" s="2">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="AM309" t="s" s="2">
-        <v>181</v>
+        <v>242</v>
       </c>
       <c r="AN309" t="s" s="2">
         <v>79</v>
@@ -39268,10 +39278,10 @@
     </row>
     <row r="310">
       <c r="A310" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="C310" s="2"/>
       <c r="D310" t="s" s="2">
@@ -39279,10 +39289,10 @@
       </c>
       <c r="E310" s="2"/>
       <c r="F310" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G310" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H310" t="s" s="2">
         <v>79</v>
@@ -39294,17 +39304,19 @@
         <v>79</v>
       </c>
       <c r="K310" t="s" s="2">
-        <v>227</v>
+        <v>172</v>
       </c>
       <c r="L310" t="s" s="2">
-        <v>384</v>
+        <v>377</v>
       </c>
       <c r="M310" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N310" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N310" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="O310" t="s" s="2">
-        <v>230</v>
+        <v>380</v>
       </c>
       <c r="P310" t="s" s="2">
         <v>79</v>
@@ -39314,7 +39326,7 @@
         <v>79</v>
       </c>
       <c r="S310" t="s" s="2">
-        <v>79</v>
+        <v>783</v>
       </c>
       <c r="T310" t="s" s="2">
         <v>79</v>
@@ -39329,13 +39341,13 @@
         <v>79</v>
       </c>
       <c r="X310" t="s" s="2">
-        <v>79</v>
+        <v>189</v>
       </c>
       <c r="Y310" t="s" s="2">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="Z310" t="s" s="2">
-        <v>79</v>
+        <v>382</v>
       </c>
       <c r="AA310" t="s" s="2">
         <v>79</v>
@@ -39353,13 +39365,13 @@
         <v>79</v>
       </c>
       <c r="AF310" t="s" s="2">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="AG310" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH310" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI310" t="s" s="2">
         <v>79</v>
@@ -39371,24 +39383,24 @@
         <v>79</v>
       </c>
       <c r="AL310" t="s" s="2">
-        <v>232</v>
+        <v>180</v>
       </c>
       <c r="AM310" t="s" s="2">
-        <v>233</v>
+        <v>181</v>
       </c>
       <c r="AN310" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO310" t="s" s="2">
-        <v>235</v>
+        <v>79</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C311" s="2"/>
       <c r="D311" t="s" s="2">
@@ -39399,7 +39411,7 @@
         <v>80</v>
       </c>
       <c r="G311" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H311" t="s" s="2">
         <v>79</v>
@@ -39411,18 +39423,18 @@
         <v>79</v>
       </c>
       <c r="K311" t="s" s="2">
-        <v>354</v>
+        <v>227</v>
       </c>
       <c r="L311" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="M311" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N311" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O311" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N311" s="2"/>
+      <c r="O311" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P311" t="s" s="2">
         <v>79</v>
       </c>
@@ -39470,13 +39482,13 @@
         <v>79</v>
       </c>
       <c r="AF311" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AG311" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH311" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI311" t="s" s="2">
         <v>79</v>
@@ -39488,24 +39500,24 @@
         <v>79</v>
       </c>
       <c r="AL311" t="s" s="2">
-        <v>79</v>
+        <v>232</v>
       </c>
       <c r="AM311" t="s" s="2">
-        <v>390</v>
+        <v>233</v>
       </c>
       <c r="AN311" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO311" t="s" s="2">
-        <v>79</v>
+        <v>235</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C312" s="2"/>
       <c r="D312" t="s" s="2">
@@ -39528,16 +39540,16 @@
         <v>79</v>
       </c>
       <c r="K312" t="s" s="2">
-        <v>121</v>
+        <v>354</v>
       </c>
       <c r="L312" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="M312" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="N312" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="O312" s="2"/>
       <c r="P312" t="s" s="2">
@@ -39587,7 +39599,7 @@
         <v>79</v>
       </c>
       <c r="AF312" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AG312" t="s" s="2">
         <v>80</v>
@@ -39596,7 +39608,7 @@
         <v>91</v>
       </c>
       <c r="AI312" t="s" s="2">
-        <v>395</v>
+        <v>79</v>
       </c>
       <c r="AJ312" t="s" s="2">
         <v>103</v>
@@ -39605,10 +39617,10 @@
         <v>79</v>
       </c>
       <c r="AL312" t="s" s="2">
-        <v>396</v>
+        <v>79</v>
       </c>
       <c r="AM312" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="AN312" t="s" s="2">
         <v>79</v>
@@ -39619,10 +39631,10 @@
     </row>
     <row r="313">
       <c r="A313" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C313" s="2"/>
       <c r="D313" t="s" s="2">
@@ -39645,20 +39657,18 @@
         <v>79</v>
       </c>
       <c r="K313" t="s" s="2">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="L313" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="M313" t="s" s="2">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="N313" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O313" t="s" s="2">
-        <v>401</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="O313" s="2"/>
       <c r="P313" t="s" s="2">
         <v>79</v>
       </c>
@@ -39682,13 +39692,13 @@
         <v>79</v>
       </c>
       <c r="X313" t="s" s="2">
-        <v>163</v>
+        <v>79</v>
       </c>
       <c r="Y313" t="s" s="2">
-        <v>402</v>
+        <v>79</v>
       </c>
       <c r="Z313" t="s" s="2">
-        <v>403</v>
+        <v>79</v>
       </c>
       <c r="AA313" t="s" s="2">
         <v>79</v>
@@ -39706,7 +39716,7 @@
         <v>79</v>
       </c>
       <c r="AF313" t="s" s="2">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="AG313" t="s" s="2">
         <v>80</v>
@@ -39715,7 +39725,7 @@
         <v>91</v>
       </c>
       <c r="AI313" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="AJ313" t="s" s="2">
         <v>103</v>
@@ -39724,24 +39734,24 @@
         <v>79</v>
       </c>
       <c r="AL313" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="AM313" t="s" s="2">
-        <v>168</v>
+        <v>396</v>
       </c>
       <c r="AN313" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO313" t="s" s="2">
-        <v>183</v>
+        <v>79</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C314" s="2"/>
       <c r="D314" t="s" s="2">
@@ -39764,19 +39774,19 @@
         <v>79</v>
       </c>
       <c r="K314" t="s" s="2">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="L314" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="M314" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="N314" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="O314" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="P314" t="s" s="2">
         <v>79</v>
@@ -39801,13 +39811,13 @@
         <v>79</v>
       </c>
       <c r="X314" t="s" s="2">
-        <v>115</v>
+        <v>163</v>
       </c>
       <c r="Y314" t="s" s="2">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="Z314" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="AA314" t="s" s="2">
         <v>79</v>
@@ -39825,7 +39835,7 @@
         <v>79</v>
       </c>
       <c r="AF314" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="AG314" t="s" s="2">
         <v>80</v>
@@ -39843,7 +39853,7 @@
         <v>79</v>
       </c>
       <c r="AL314" t="s" s="2">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="AM314" t="s" s="2">
         <v>168</v>
@@ -39852,15 +39862,15 @@
         <v>79</v>
       </c>
       <c r="AO314" t="s" s="2">
-        <v>79</v>
+        <v>183</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="C315" s="2"/>
       <c r="D315" t="s" s="2">
@@ -39871,7 +39881,7 @@
         <v>80</v>
       </c>
       <c r="G315" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H315" t="s" s="2">
         <v>79</v>
@@ -39883,18 +39893,20 @@
         <v>79</v>
       </c>
       <c r="K315" t="s" s="2">
-        <v>354</v>
+        <v>172</v>
       </c>
       <c r="L315" t="s" s="2">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="M315" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="N315" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O315" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="O315" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P315" t="s" s="2">
         <v>79</v>
       </c>
@@ -39918,13 +39930,13 @@
         <v>79</v>
       </c>
       <c r="X315" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="Y315" t="s" s="2">
-        <v>79</v>
+        <v>410</v>
       </c>
       <c r="Z315" t="s" s="2">
-        <v>79</v>
+        <v>411</v>
       </c>
       <c r="AA315" t="s" s="2">
         <v>79</v>
@@ -39942,16 +39954,16 @@
         <v>79</v>
       </c>
       <c r="AF315" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="AG315" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH315" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI315" t="s" s="2">
-        <v>417</v>
+        <v>79</v>
       </c>
       <c r="AJ315" t="s" s="2">
         <v>103</v>
@@ -39960,10 +39972,10 @@
         <v>79</v>
       </c>
       <c r="AL315" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="AM315" t="s" s="2">
-        <v>419</v>
+        <v>168</v>
       </c>
       <c r="AN315" t="s" s="2">
         <v>79</v>
@@ -39974,10 +39986,10 @@
     </row>
     <row r="316">
       <c r="A316" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="C316" s="2"/>
       <c r="D316" t="s" s="2">
@@ -39988,7 +40000,7 @@
         <v>80</v>
       </c>
       <c r="G316" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H316" t="s" s="2">
         <v>79</v>
@@ -40000,20 +40012,18 @@
         <v>79</v>
       </c>
       <c r="K316" t="s" s="2">
-        <v>172</v>
+        <v>354</v>
       </c>
       <c r="L316" t="s" s="2">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="M316" t="s" s="2">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="N316" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O316" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="O316" s="2"/>
       <c r="P316" t="s" s="2">
         <v>79</v>
       </c>
@@ -40037,13 +40047,13 @@
         <v>79</v>
       </c>
       <c r="X316" t="s" s="2">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="Y316" t="s" s="2">
-        <v>425</v>
+        <v>79</v>
       </c>
       <c r="Z316" t="s" s="2">
-        <v>426</v>
+        <v>79</v>
       </c>
       <c r="AA316" t="s" s="2">
         <v>79</v>
@@ -40061,13 +40071,13 @@
         <v>79</v>
       </c>
       <c r="AF316" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="AG316" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH316" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI316" t="s" s="2">
         <v>417</v>
@@ -40079,10 +40089,10 @@
         <v>79</v>
       </c>
       <c r="AL316" t="s" s="2">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="AM316" t="s" s="2">
-        <v>168</v>
+        <v>419</v>
       </c>
       <c r="AN316" t="s" s="2">
         <v>79</v>
@@ -40093,10 +40103,10 @@
     </row>
     <row r="317">
       <c r="A317" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C317" s="2"/>
       <c r="D317" t="s" s="2">
@@ -40107,7 +40117,7 @@
         <v>80</v>
       </c>
       <c r="G317" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H317" t="s" s="2">
         <v>79</v>
@@ -40119,18 +40129,20 @@
         <v>79</v>
       </c>
       <c r="K317" t="s" s="2">
-        <v>82</v>
+        <v>172</v>
       </c>
       <c r="L317" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="M317" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="N317" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O317" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="O317" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P317" t="s" s="2">
         <v>79</v>
       </c>
@@ -40154,13 +40166,13 @@
         <v>79</v>
       </c>
       <c r="X317" t="s" s="2">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="Y317" t="s" s="2">
-        <v>79</v>
+        <v>425</v>
       </c>
       <c r="Z317" t="s" s="2">
-        <v>79</v>
+        <v>426</v>
       </c>
       <c r="AA317" t="s" s="2">
         <v>79</v>
@@ -40178,16 +40190,16 @@
         <v>79</v>
       </c>
       <c r="AF317" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="AG317" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH317" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI317" t="s" s="2">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="AJ317" t="s" s="2">
         <v>103</v>
@@ -40196,15 +40208,132 @@
         <v>79</v>
       </c>
       <c r="AL317" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AM317" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AN317" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO317" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="B318" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="C318" s="2"/>
+      <c r="D318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E318" s="2"/>
+      <c r="F318" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G318" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K318" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L318" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M318" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="N318" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="O318" s="2"/>
+      <c r="P318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q318" s="2"/>
+      <c r="R318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF318" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AG318" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH318" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI318" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AJ318" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL318" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AM317" t="s" s="2">
+      <c r="AM318" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AN317" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO317" t="s" s="2">
+      <c r="AN318" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO318" t="s" s="2">
         <v>79</v>
       </c>
     </row>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T07:50:08+00:00</t>
+    <t>2026-02-13T12:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T12:44:21+00:00</t>
+    <t>2026-02-16T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1132,7 +1132,7 @@
     <t>The root of the sections that make up the composition.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:code}
+    <t xml:space="preserve">value:code}
 </t>
   </si>
   <si>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T08:31:54+00:00</t>
+    <t>2026-02-16T11:13:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T11:13:42+00:00</t>
+    <t>2026-02-17T09:00:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-main/StructureDefinition-at-aps-composition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T09:00:43+00:00</t>
+    <t>2026-09-01T07:40:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
